--- a/剪枝结果-飞书.xlsx
+++ b/剪枝结果-飞书.xlsx
@@ -5053,7 +5053,9 @@
       <c r="G6" s="20" t="n"/>
       <c r="H6" s="20" t="n"/>
       <c r="I6" s="20" t="n"/>
-      <c r="J6" s="20" t="n"/>
+      <c r="J6" s="20" t="n">
+        <v>8.381324807831589</v>
+      </c>
       <c r="K6" s="18" t="inlineStr">
         <is>
           <t>N/A</t>

--- a/剪枝结果-飞书.xlsx
+++ b/剪枝结果-飞书.xlsx
@@ -4955,15 +4955,33 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
-      <c r="J4" s="7" t="n"/>
+      <c r="B4" s="7" t="n">
+        <v>0.8615</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>0.8303</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>0.7072000000000001</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>0.8089</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>0.5512</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>7.130842820721178</v>
+      </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -4996,15 +5014,33 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
+      <c r="B5" s="7" t="n">
+        <v>0.8563</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>0.8231000000000001</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>0.7823</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>0.6938</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>0.7074</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>7.641295233837159</v>
+      </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5037,16 +5073,32 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
+      <c r="B6" s="7" t="n">
+        <v>0.8459</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>0.7942</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>0.7566000000000001</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>0.7167</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>0.7559</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.5111</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.6889</v>
+      </c>
       <c r="J6" s="7" t="n">
-        <v>8.381324807831589</v>
+        <v>8.380624525273207</v>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
@@ -5080,15 +5132,33 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
+      <c r="B7" s="7" t="n">
+        <v>0.8416</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0.7059</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>0.7056</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>0.7231</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0.4855</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0.6675</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>10.26637317144166</v>
+      </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -7188,11 +7258,21 @@
       <c r="J12" s="7" t="n">
         <v>149.634</v>
       </c>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="7" t="n"/>
+      <c r="K12" s="7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>1.16192250652754</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>1.046480626631885</v>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -7227,11 +7307,21 @@
       <c r="J13" s="7" t="n">
         <v>308.1079</v>
       </c>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
-      <c r="O13" s="7" t="n"/>
+      <c r="K13" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>0.09926719423150988</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>0.4418167985578775</v>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -8195,19 +8285,19 @@
         <v>208.087378819646</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>7.8</v>
+        <v>14.7</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0</v>
+        <v>0.8579999999999999</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>0</v>
+        <v>0.5463659668548543</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>1.95</v>
+        <v>4.146091491713713</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -11704,16 +11794,32 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
+      <c r="B4" s="7" t="n">
+        <v>0.6516999999999999</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>0.5306999999999999</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>0.6738</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>0.6431</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>0.5577</v>
+      </c>
       <c r="J4" s="7" t="n">
-        <v>9.92</v>
+        <v>9.903120645000332</v>
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
@@ -11747,15 +11853,33 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
+      <c r="B5" s="7" t="n">
+        <v>0.5823</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>0.4321</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>0.4901</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>0.4781</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>0.4387</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>59.03732498106265</v>
+      </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -11788,15 +11912,33 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
+      <c r="B6" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>0.5306999999999999</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>0.2822</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>0.5122</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>0.2559</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.2628</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>24424.98163865017</v>
+      </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -11829,15 +11971,33 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
+      <c r="B7" s="7" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>0.4729</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>0.5241</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0.2602</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>27021.06192441845</v>
+      </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
           <t>N/A</t>

--- a/剪枝结果-飞书.xlsx
+++ b/剪枝结果-飞书.xlsx
@@ -9310,11 +9310,21 @@
       <c r="J10" s="7" t="n">
         <v>48.7191</v>
       </c>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="n"/>
-      <c r="O10" s="7" t="n"/>
+      <c r="K10" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>75.124</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>67.47999999999999</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>63.02515104147519</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>69.15728776036879</v>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="inlineStr">

--- a/剪枝结果-飞书.xlsx
+++ b/剪枝结果-飞书.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结构化_flap_GPU" sheetId="1" state="visible" r:id="rId1"/>
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,12 +48,6 @@
       <family val="2"/>
       <color rgb="FF000000"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -150,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -161,10 +155,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -187,6 +181,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2143,11 +2140,21 @@
       <c r="J10" s="7" t="n">
         <v>8.5025</v>
       </c>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="n"/>
-      <c r="O10" s="7" t="n"/>
+      <c r="K10" s="7" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>84.42</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>84.84</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>81.48153450189396</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>84.33538362547348</v>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -2182,11 +2189,21 @@
       <c r="J11" s="7" t="n">
         <v>9.003</v>
       </c>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="n"/>
-      <c r="O11" s="7" t="n"/>
+      <c r="K11" s="7" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>83.77</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>80.95999999999999</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>80.1948625965919</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <v>82.68121564914797</v>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -2221,11 +2238,21 @@
       <c r="J12" s="7" t="n">
         <v>9.971299999999999</v>
       </c>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="7" t="n"/>
+      <c r="K12" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>79.56</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>77.58296242630071</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>80.97074060657518</v>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -2260,11 +2287,21 @@
       <c r="J13" s="7" t="n">
         <v>19.1535</v>
       </c>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
-      <c r="O13" s="7" t="n"/>
+      <c r="K13" s="7" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>72.86399999999999</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>70.89963423711968</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>67.09090855927992</v>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -4253,11 +4290,21 @@
       <c r="J10" s="7" t="n">
         <v>8.648300000000001</v>
       </c>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="n"/>
-      <c r="O10" s="7" t="n"/>
+      <c r="K10" s="7" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>84.37</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>84.76000000000001</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>81.50727932374508</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>84.50931983093628</v>
+      </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -4292,11 +4339,21 @@
       <c r="J11" s="7" t="n">
         <v>8.875500000000001</v>
       </c>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="n"/>
-      <c r="O11" s="7" t="n"/>
+      <c r="K11" s="7" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>83.35600000000001</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>79.52789197803581</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <v>80.97097299450895</v>
+      </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -4331,11 +4388,21 @@
       <c r="J12" s="7" t="n">
         <v>9.862500000000001</v>
       </c>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="7" t="n"/>
+      <c r="K12" s="7" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>78.08800000000001</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>55.16</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>75.67577593673764</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>73.4059439841844</v>
+      </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -5261,20 +5328,48 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="n"/>
-      <c r="O10" s="7" t="n"/>
+      <c r="B10" s="7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>0.8195</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0.7658</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>0.7009</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>0.7243000000000001</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0.4949</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.6882</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>8.564035972707829</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>84.506</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>85.31999999999999</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>81.81186215414453</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>84.68446553853613</v>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -5282,20 +5377,48 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="n"/>
-      <c r="O11" s="7" t="n"/>
+      <c r="B11" s="7" t="n">
+        <v>0.8627</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>0.8123</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>0.6856</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0.4556</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.6676</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>8.860047193871495</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>82.836</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>74.31999999999999</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>79.90026389391663</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <v>80.68906597347916</v>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -5303,20 +5426,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="7" t="n"/>
+      <c r="B12" s="7" t="n">
+        <v>0.8661</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>0.8014</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0.7169</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>0.6969</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>0.6322</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.6498</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>9.677255053096868</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>80.55799999999999</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>72.52</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>76.25623885287102</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>78.40855971321776</v>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -5324,20 +5475,48 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
-      <c r="O13" s="7" t="n"/>
+      <c r="B13" s="7" t="n">
+        <v>0.8505</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>0.6551</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>0.6764</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>0.6343</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>0.6307</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>11.83292822474368</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>70.74600000000001</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>70.04562400459908</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>65.39790600114976</v>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -6179,11 +6358,21 @@
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
       <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="n"/>
-      <c r="O10" s="7" t="n"/>
+      <c r="K10" s="7" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>84.31400000000001</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>84.72</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>81.58745746640041</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>84.4303643666001</v>
+      </c>
     </row>
     <row r="11" ht="19.5" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -6200,11 +6389,21 @@
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
       <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="n"/>
-      <c r="O11" s="7" t="n"/>
+      <c r="K11" s="7" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>82.742</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>72.44</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>79.89145068286729</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <v>80.16836267071682</v>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -9359,11 +9558,21 @@
       <c r="J11" s="7" t="n">
         <v>229.4795</v>
       </c>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="n"/>
-      <c r="O11" s="7" t="n"/>
+      <c r="K11" s="7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <v>2.35</v>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -9398,11 +9607,21 @@
       <c r="J12" s="7" t="n">
         <v>504.9453</v>
       </c>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="7" t="n"/>
+      <c r="K12" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>0.1825</v>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -9437,11 +9656,21 @@
       <c r="J13" s="7" t="n">
         <v>5167.8292</v>
       </c>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
-      <c r="O13" s="7" t="n"/>
+      <c r="K13" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>0.02231345947875759</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>0.4605783648696894</v>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -9859,7 +10088,7 @@
     <col width="12.71928571428571" bestFit="1" customWidth="1" style="11" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="21.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>稀疏率</t>
@@ -9936,7 +10165,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1">
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Qwen2.5-7b</t>
@@ -9957,7 +10186,7 @@
       <c r="N2" s="12" t="n"/>
       <c r="O2" s="13" t="n"/>
     </row>
-    <row r="3" ht="22" customHeight="1">
+    <row r="3" ht="19.5" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>0%</t>
@@ -10016,21 +10245,39 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
+    <row r="4" ht="19.5" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
-      <c r="J4" s="7" t="n"/>
+      <c r="B4" s="7" t="n">
+        <v>0.8428</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>0.8159</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>0.7606000000000001</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>0.6882</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>0.6999</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>0.4744</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>0.6723</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>8.597291744520142</v>
+      </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -10057,21 +10304,39 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
+    <row r="5" ht="19.5" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
+      <c r="B5" s="7" t="n">
+        <v>0.5563</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>0.5415</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>0.5209</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>0.2201</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>299.4708396607053</v>
+      </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -10098,21 +10363,39 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="19.5" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
+      <c r="B6" s="7" t="n">
+        <v>0.5734</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>0.5306999999999999</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>0.2682</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>0.5209</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>0.2723</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.2201</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>1233.96350527053</v>
+      </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -10139,21 +10422,39 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
+    <row r="7" ht="19.5" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
+      <c r="B7" s="7" t="n">
+        <v>0.5352</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0.2647</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>0.4941</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0.2346</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>1955.666749472303</v>
+      </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -10180,7 +10481,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="20.25" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Qwen2.5-VL-7b</t>
@@ -10201,7 +10502,7 @@
       <c r="N8" s="12" t="n"/>
       <c r="O8" s="13" t="n"/>
     </row>
-    <row r="9" ht="22" customHeight="1">
+    <row r="9" ht="19.5" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>0%</t>
@@ -10250,89 +10551,201 @@
         <v>84.78103060126868</v>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
+    <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="n"/>
-      <c r="O10" s="7" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
+      <c r="B10" s="7" t="n">
+        <v>0.8404</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>0.6756</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>0.6355</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.6394</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>10.20707123473386</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>82.334</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>71.64</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>74.37087430819756</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>74.56121857704939</v>
+      </c>
+    </row>
+    <row r="11" ht="19.5" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="n"/>
-      <c r="O11" s="7" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
+      <c r="B11" s="7" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>0.6968</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0.4064</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>0.5406</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0.2432</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.4659</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>37.16491982585389</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>0.03570153516601214</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <v>0.04042538379150304</v>
+      </c>
+    </row>
+    <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="7" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
+      <c r="B12" s="7" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0.2679</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>0.4949</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0.2432</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>1087.875123083332</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>2.475</v>
+      </c>
+    </row>
+    <row r="13" ht="19.5" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
-      <c r="O13" s="7" t="n"/>
+      <c r="B13" s="7" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>0.5306999999999999</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>0.5028</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>0.2723</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0.2381</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>1496.983133754837</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>1.175</v>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -12110,20 +12523,48 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="n"/>
-      <c r="O10" s="7" t="n"/>
+      <c r="B10" s="7" t="n">
+        <v>0.6624</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>0.6606</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0.6605</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>0.6402</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.5717</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>10.82890680166059</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>71.84</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>39.52</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>42.38735922280916</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>54.73683980570229</v>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -12131,20 +12572,48 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="n"/>
-      <c r="O11" s="7" t="n"/>
+      <c r="B11" s="7" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>0.5018</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0.4579</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>0.5036</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>0.4966</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.4431</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>39.3944430262746</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>7.720000000000001</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>8.268267090508816</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <v>19.4970667726272</v>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -12152,20 +12621,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="7" t="n"/>
+      <c r="B12" s="7" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>0.5054</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>0.4791</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0.2602</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>1001335.383001926</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>0.6179810468692259</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>0.4504952617173065</v>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -12173,20 +12670,48 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
-      <c r="O13" s="7" t="n"/>
+      <c r="B13" s="7" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>0.5306999999999999</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>0.5012</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>0.2576</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>844287.7174333771</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0.05599999999999999</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>0.1785076758300607</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>0.3936269189575152</v>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -13010,11 +13535,21 @@
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
       <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="n"/>
-      <c r="O10" s="7" t="n"/>
+      <c r="K10" s="7" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>72.03200000000001</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>42.16473219293489</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>54.87418304823373</v>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -13031,11 +13566,21 @@
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
       <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="n"/>
-      <c r="O11" s="7" t="n"/>
+      <c r="K11" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>12.056</v>
+      </c>
+      <c r="M11" s="14" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N11" s="14" t="n">
+        <v>0.524276112248895</v>
+      </c>
+      <c r="O11" s="14" t="n">
+        <v>12.18506902806222</v>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -13052,11 +13597,21 @@
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="7" t="n"/>
       <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="7" t="n"/>
+      <c r="K12" s="7" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>0.3490507022540928</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>1.912262675563523</v>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -13073,11 +13628,21 @@
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
-      <c r="O13" s="7" t="n"/>
+      <c r="K13" s="7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>0.02304141631281634</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>1.633760354078204</v>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">

--- a/剪枝结果-飞书.xlsx
+++ b/剪枝结果-飞书.xlsx
@@ -1255,15 +1255,33 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="B15" s="9" t="n">
+        <v>0.8661</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>0.7798</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.6756</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0.8098</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>0.6947</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>9.10982977931196</v>
+      </c>
       <c r="K15" s="7" t="n"/>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
@@ -1276,15 +1294,33 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>0.6217</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>0.6065</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.6084000000000001</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>0.6637999999999999</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>0.6738</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>0.4343</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>0.5689</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>11.04896363576379</v>
+      </c>
       <c r="K16" s="7" t="n"/>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
@@ -3405,15 +3441,33 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="B15" s="9" t="n">
+        <v>0.8661</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>0.7798</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.6756</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0.8098</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>0.6947</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>9.10982977931196</v>
+      </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
@@ -3426,15 +3480,33 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>0.8624000000000001</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>0.7544999999999999</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.7496</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>0.6803</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>0.8038999999999999</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>0.5589</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>0.6899</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>9.127485388339545</v>
+      </c>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
@@ -4437,11 +4509,21 @@
       <c r="J13" s="7" t="n">
         <v>12.6795</v>
       </c>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
-      <c r="O13" s="7" t="n"/>
+      <c r="K13" s="14" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>72.274</v>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="N13" s="14" t="n">
+        <v>70.60266563167013</v>
+      </c>
+      <c r="O13" s="14" t="n">
+        <v>65.59416640791754</v>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -5545,15 +5627,33 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="B15" s="9" t="n">
+        <v>0.8661</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>0.7798</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.6756</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0.8098</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>0.6947</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>9.10982977931196</v>
+      </c>
       <c r="K15" s="7" t="n"/>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
@@ -5566,15 +5666,33 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>0.8657</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>0.7581</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.7487</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>0.6756</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>0.8081</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>0.5648</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>0.6921</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>9.124557592179945</v>
+      </c>
       <c r="K16" s="7" t="n"/>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
@@ -6420,11 +6538,21 @@
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="7" t="n"/>
       <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="7" t="n"/>
+      <c r="K12" s="7" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>80.828</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>66.92</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>76.13046309551542</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>77.06911577387885</v>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -6441,11 +6569,21 @@
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
-      <c r="O13" s="7" t="n"/>
+      <c r="K13" s="7" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>70.41799999999999</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>39.08</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>71.122120897819</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>65.10503022445475</v>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -8624,15 +8762,33 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="B15" s="9" t="n">
+        <v>0.8661</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>0.7798</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.6756</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0.8098</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>0.6947</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>9.10982977931196</v>
+      </c>
       <c r="K15" s="7" t="n"/>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
@@ -8645,15 +8801,33 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>0.5957</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.5278</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>0.6654</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>0.4206</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>0.5397999999999999</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>15.13763761771854</v>
+      </c>
       <c r="K16" s="7" t="n"/>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
@@ -10774,15 +10948,33 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="B15" s="9" t="n">
+        <v>0.8661</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>0.7798</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.6756</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0.8098</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>0.6947</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>9.10982977931196</v>
+      </c>
       <c r="K15" s="7" t="n"/>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
@@ -10795,15 +10987,33 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>0.7795</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>0.6462</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.6089</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>0.6212</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>0.6578000000000001</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>0.5838</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>12.58221241542789</v>
+      </c>
       <c r="K16" s="7" t="n"/>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
@@ -11326,15 +11536,33 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
-      <c r="J4" s="7" t="n"/>
+      <c r="B4" s="14" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>0.8159</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>0.6575</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>0.4684</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>0.6578000000000001</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>8.869259822821711</v>
+      </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -11367,15 +11595,33 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
+      <c r="B5" s="14" t="n">
+        <v>0.6422</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>0.5884</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0.4722</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0.4713</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>25.99775523308284</v>
+      </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -11408,15 +11654,33 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
+      <c r="B6" s="14" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>0.5235</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>0.2652</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>0.4957</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>0.2457</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>1523.032221504005</v>
+      </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -11449,15 +11713,33 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
+      <c r="B7" s="14" t="n">
+        <v>0.4807</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>0.5107</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>0.2346</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>2314.725688588353</v>
+      </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -12740,15 +13022,33 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="B15" s="9" t="n">
+        <v>0.8661</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>0.7798</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.6756</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0.8098</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>0.6947</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>9.10982977931196</v>
+      </c>
       <c r="K15" s="7" t="n"/>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
@@ -12761,15 +13061,33 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>0.6388</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>0.7978</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>0.5754</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>0.5282</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>0.5391</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>204.5968130204869</v>
+      </c>
       <c r="K16" s="7" t="n"/>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
@@ -13292,15 +13610,33 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
-      <c r="J4" s="7" t="n"/>
+      <c r="B4" s="7" t="n">
+        <v>0.6468</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>0.5306999999999999</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>0.5508999999999999</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>0.6414</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>0.5568</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>9.920283453197349</v>
+      </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -13333,15 +13669,33 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
+      <c r="B5" s="7" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>0.5306999999999999</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>0.4188</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>0.4972</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>0.4372</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>74.31369957023551</v>
+      </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -13374,15 +13728,33 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
+      <c r="B6" s="7" t="n">
+        <v>0.6202</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>0.5415</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>0.2666</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>0.2622</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.2602</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>44376.21607915003</v>
+      </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -13415,15 +13787,33 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
+      <c r="B7" s="7" t="n">
+        <v>0.6119</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>0.5379</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0.2629</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>0.5012</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>0.2559</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0.2423</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>13125.10576403416</v>
+      </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -13526,15 +13916,33 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
+      <c r="B10" s="7" t="n">
+        <v>0.6627</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>0.6534</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0.6608000000000001</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>0.5967</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>0.6418</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.5724</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>10.82755569617407</v>
+      </c>
       <c r="K10" s="7" t="n">
         <v>65.7</v>
       </c>
@@ -13557,15 +13965,33 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
+      <c r="B11" s="7" t="n">
+        <v>0.5443</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>0.5235</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0.4466</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>0.5012</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0.2654</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.4374</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>39.42792788310279</v>
+      </c>
       <c r="K11" s="14" t="n">
         <v>36</v>
       </c>
@@ -13588,15 +14014,33 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
+      <c r="B12" s="7" t="n">
+        <v>0.5131</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>0.5125999999999999</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>0.4949</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0.2201</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>638.3575864992241</v>
+      </c>
       <c r="K12" s="7" t="n">
         <v>7.3</v>
       </c>
@@ -13619,15 +14063,33 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
+      <c r="B13" s="14" t="n">
+        <v>0.4841</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0.5328000000000001</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>0.2883</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0.2363</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>3618.44541907442</v>
+      </c>
       <c r="K13" s="7" t="n">
         <v>6.4</v>
       </c>
@@ -14746,15 +15208,33 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="B15" s="9" t="n">
+        <v>0.8661</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>0.7798</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.6756</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0.8098</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>0.6947</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>9.10982977931196</v>
+      </c>
       <c r="K15" s="7" t="n"/>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
@@ -14767,15 +15247,33 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>0.8663999999999999</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>0.7581</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.7448</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>0.8102</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>0.5555</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>0.6915</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>9.123142806408664</v>
+      </c>
       <c r="K16" s="7" t="n"/>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>

--- a/剪枝结果-飞书.xlsx
+++ b/剪枝结果-飞书.xlsx
@@ -6274,15 +6274,33 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
+      <c r="B5" s="14" t="n">
+        <v>0.8529</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>0.8159</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>0.7811</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>0.7056</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0.7875</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>0.5324</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0.7076</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>7.633651267741855</v>
+      </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6315,15 +6333,33 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
+      <c r="B6" s="14" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>0.7574</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>0.7174</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>0.7395</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>0.5017</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>0.6843</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>8.365449841181379</v>
+      </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6356,15 +6392,33 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
+      <c r="B7" s="14" t="n">
+        <v>0.8483000000000001</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>0.7834</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>0.6961000000000001</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>0.7075</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>0.4582</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0.6594</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>10.18265472054943</v>
+      </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6467,15 +6521,33 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
+      <c r="B10" s="14" t="n">
+        <v>0.8691</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>0.8195</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>0.7665999999999999</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>0.7000999999999999</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>0.7231</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>0.4949</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>0.6873</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>8.583787658756737</v>
+      </c>
       <c r="K10" s="7" t="n">
         <v>87.09999999999999</v>
       </c>
@@ -6498,15 +6570,33 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
+      <c r="B11" s="14" t="n">
+        <v>0.8606</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>0.8159</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>0.6882</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0.6772</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0.4539</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>0.6663</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>8.902047112463737</v>
+      </c>
       <c r="K11" s="7" t="n">
         <v>85.59999999999999</v>
       </c>
@@ -6529,15 +6619,33 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
+      <c r="B12" s="14" t="n">
+        <v>0.8599</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>0.7171</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>0.6882</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>0.6492</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>9.793435793805299</v>
+      </c>
       <c r="K12" s="7" t="n">
         <v>84.40000000000001</v>
       </c>
@@ -6560,15 +6668,33 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
+      <c r="B13" s="14" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>0.8087</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>0.6534</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0.6709000000000001</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0.3882</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>0.6254999999999999</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>11.92136056487174</v>
+      </c>
       <c r="K13" s="7" t="n">
         <v>79.8</v>
       </c>
@@ -11842,20 +11968,48 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="n"/>
-      <c r="O10" s="7" t="n"/>
+      <c r="B10" s="14" t="n">
+        <v>0.7985</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>0.8087</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>0.6893</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>0.6535</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>0.6418</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>0.6261</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>10.62726373722229</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="L10" s="14" t="n">
+        <v>83.09400000000001</v>
+      </c>
+      <c r="M10" s="14" t="n">
+        <v>80.36</v>
+      </c>
+      <c r="N10" s="14" t="n">
+        <v>77.15551739447334</v>
+      </c>
+      <c r="O10" s="14" t="n">
+        <v>81.35237934861834</v>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -11863,20 +12017,48 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="n"/>
-      <c r="O11" s="7" t="n"/>
+      <c r="B11" s="14" t="n">
+        <v>0.6535</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>0.5776</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>0.5091</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0.2483</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>42.10160959652763</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="14" t="n">
+        <v>0.01785076758300607</v>
+      </c>
+      <c r="O11" s="14" t="n">
+        <v>0.1044626918957515</v>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -11884,20 +12066,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="7" t="n"/>
+      <c r="B12" s="14" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>0.5379</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>0.2684</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>0.4917</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>0.2363</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>888.4766431411424</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L12" s="14" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="14" t="n">
+        <v>2.44</v>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -11905,20 +12115,48 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
-      <c r="O13" s="7" t="n"/>
+      <c r="B13" s="14" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>0.5199</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>0.2682</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0.5051</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0.2295</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>1255.084409510152</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="N13" s="14" t="n">
+        <v>0.01785076758300607</v>
+      </c>
+      <c r="O13" s="14" t="n">
+        <v>2.409462691895751</v>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">

--- a/剪枝结果-飞书.xlsx
+++ b/剪枝结果-飞书.xlsx
@@ -144,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -182,6 +182,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1669,20 +1672,48 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
-      <c r="N23" s="7" t="n"/>
-      <c r="O23" s="7" t="n"/>
+      <c r="B23" s="14" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>0.5343</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>0.4032</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>0.2662</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>27.4986019508921</v>
+      </c>
+      <c r="K23" s="14" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="14" t="n">
+        <v>0.01785076758300607</v>
+      </c>
+      <c r="O23" s="14" t="n">
+        <v>7.104462691895751</v>
+      </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
@@ -1690,20 +1721,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="7" t="n"/>
-      <c r="N24" s="7" t="n"/>
-      <c r="O24" s="7" t="n"/>
+      <c r="B24" s="14" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>0.5054</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>0.4949</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0.2398</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>127.1807499338678</v>
+      </c>
+      <c r="K24" s="14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="14" t="n">
+        <v>2.056040554019864</v>
+      </c>
+      <c r="O24" s="14" t="n">
+        <v>1.354010138504966</v>
+      </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -1711,20 +1770,48 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="7" t="n"/>
-      <c r="L25" s="7" t="n"/>
-      <c r="M25" s="7" t="n"/>
-      <c r="N25" s="7" t="n"/>
-      <c r="O25" s="7" t="n"/>
+      <c r="B25" s="14" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>0.2636</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>0.5083</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.2723</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0.2534</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>1342.462248262452</v>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="14" t="n">
+        <v>0.08925383791503035</v>
+      </c>
+      <c r="O25" s="14" t="n">
+        <v>0.02731345947875759</v>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -2731,20 +2818,58 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="14" t="n"/>
-      <c r="H20" s="14" t="n"/>
-      <c r="I20" s="14" t="n"/>
-      <c r="J20" s="14" t="n"/>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
-      <c r="O20" s="8" t="n"/>
+      <c r="B20" s="14" t="n">
+        <v>0.8653999999999999</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>0.7581</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>0.6811</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>0.8102</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>0.6913</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>9.112280436493673</v>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
@@ -3778,15 +3903,33 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="14" t="n"/>
-      <c r="J8" s="14" t="n"/>
+      <c r="B8" s="14" t="n">
+        <v>0.8489</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>0.6693</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0.6543</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>0.7024</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>0.6471</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>11.08520825383899</v>
+      </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -3819,15 +3962,33 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
-      <c r="J9" s="14" t="n"/>
+      <c r="B9" s="14" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>0.7906</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>0.7101</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0.7593</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>0.5154</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0.6787</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>9.572334093230605</v>
+      </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -4220,20 +4381,58 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="14" t="n"/>
-      <c r="H20" s="14" t="n"/>
-      <c r="I20" s="14" t="n"/>
-      <c r="J20" s="14" t="n"/>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
-      <c r="O20" s="8" t="n"/>
+      <c r="B20" s="14" t="n">
+        <v>0.8624000000000001</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>0.7544999999999999</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>0.7496</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>0.6803</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>0.8038999999999999</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0.5589</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>0.6899</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>9.127485388339545</v>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
@@ -4418,15 +4617,33 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="14" t="n"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="14" t="n"/>
-      <c r="H24" s="14" t="n"/>
-      <c r="I24" s="14" t="n"/>
-      <c r="J24" s="14" t="n"/>
+      <c r="B24" s="14" t="n">
+        <v>0.8024</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>0.6209</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>0.6025</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>0.6646</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>0.7201</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0.4599</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>0.6041</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>13.83688651607962</v>
+      </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -4619,20 +4836,48 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="9" t="n"/>
-      <c r="L29" s="7" t="n"/>
-      <c r="M29" s="7" t="n"/>
-      <c r="N29" s="7" t="n"/>
-      <c r="O29" s="7" t="n"/>
+      <c r="B29" s="14" t="n">
+        <v>0.8737</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>0.8087</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>0.7423</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>0.7301</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>0.7824</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>0.5794</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>0.7058</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>8.674771433161489</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>79.91800000000001</v>
+      </c>
+      <c r="M29" s="14" t="n">
+        <v>76.28</v>
+      </c>
+      <c r="N29" s="14" t="n">
+        <v>80.8428228174611</v>
+      </c>
+      <c r="O29" s="14" t="n">
+        <v>81.06020570436527</v>
+      </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
@@ -4640,20 +4885,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="9" t="n"/>
-      <c r="L30" s="7" t="n"/>
-      <c r="M30" s="7" t="n"/>
-      <c r="N30" s="7" t="n"/>
-      <c r="O30" s="7" t="n"/>
+      <c r="B30" s="14" t="n">
+        <v>0.8679</v>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>0.7834</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>0.7063</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>0.7096</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>0.7971</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>0.5589</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>0.6907</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>9.921894189414953</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="L30" s="14" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="M30" s="14" t="n">
+        <v>55.67999999999999</v>
+      </c>
+      <c r="N30" s="14" t="n">
+        <v>75.75673458075049</v>
+      </c>
+      <c r="O30" s="14" t="n">
+        <v>73.01418364518763</v>
+      </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
@@ -4661,20 +4934,48 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="9" t="n"/>
-      <c r="K31" s="9" t="n"/>
-      <c r="L31" s="7" t="n"/>
-      <c r="M31" s="7" t="n"/>
-      <c r="N31" s="7" t="n"/>
-      <c r="O31" s="7" t="n"/>
+      <c r="B31" s="14" t="n">
+        <v>0.8541</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>0.7834</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>0.6368</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>0.6796</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>0.7327</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>0.6494</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>12.81614639754308</v>
+      </c>
+      <c r="K31" s="14" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="L31" s="14" t="n">
+        <v>70.80200000000001</v>
+      </c>
+      <c r="M31" s="14" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="N31" s="14" t="n">
+        <v>60.53951918924029</v>
+      </c>
+      <c r="O31" s="14" t="n">
+        <v>62.87037979731006</v>
+      </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
@@ -5765,20 +6066,58 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="14" t="n"/>
-      <c r="H20" s="14" t="n"/>
-      <c r="I20" s="14" t="n"/>
-      <c r="J20" s="14" t="n"/>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
-      <c r="O20" s="8" t="n"/>
+      <c r="B20" s="14" t="n">
+        <v>0.8639</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>0.7497</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>0.6796</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>0.8098</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>0.6945</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>9.115361149685219</v>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
@@ -6812,15 +7151,33 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="14" t="n"/>
-      <c r="J8" s="14" t="n"/>
+      <c r="B8" s="14" t="n">
+        <v>0.8421999999999999</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>0.6854</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0.6851</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>0.7323</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0.4829</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>0.6633</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>10.46886604737493</v>
+      </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -7062,20 +7419,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="14" t="n"/>
-      <c r="I14" s="14" t="n"/>
-      <c r="J14" s="14" t="n"/>
-      <c r="K14" s="8" t="n"/>
-      <c r="L14" s="8" t="n"/>
-      <c r="M14" s="8" t="n"/>
-      <c r="N14" s="8" t="n"/>
-      <c r="O14" s="8" t="n"/>
+      <c r="B14" s="14" t="n">
+        <v>0.8661</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>0.8014</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>0.7169</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>0.6969</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>0.6322</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>0.6498</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>9.677255053096868</v>
+      </c>
+      <c r="K14" s="15" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>80.55799999999999</v>
+      </c>
+      <c r="M14" s="15" t="n">
+        <v>72.52</v>
+      </c>
+      <c r="N14" s="15" t="n">
+        <v>76.25623885287102</v>
+      </c>
+      <c r="O14" s="15" t="n">
+        <v>78.40855971321776</v>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
@@ -7254,20 +7639,58 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="14" t="n"/>
-      <c r="H20" s="14" t="n"/>
-      <c r="I20" s="14" t="n"/>
-      <c r="J20" s="14" t="n"/>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
-      <c r="O20" s="8" t="n"/>
+      <c r="B20" s="14" t="n">
+        <v>0.8657</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>0.7581</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>0.7487</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>0.6756</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>0.8081</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0.5648</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>0.6921</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>9.124557592179945</v>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
@@ -7452,15 +7875,33 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="14" t="n"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="14" t="n"/>
-      <c r="H24" s="14" t="n"/>
-      <c r="I24" s="14" t="n"/>
-      <c r="J24" s="14" t="n"/>
+      <c r="B24" s="14" t="n">
+        <v>0.8376</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>0.6534</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>0.6281</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>0.6819</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>0.7214</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>0.6253</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>12.8279188900666</v>
+      </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -7653,20 +8094,48 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="7" t="n"/>
-      <c r="L29" s="7" t="n"/>
-      <c r="M29" s="7" t="n"/>
-      <c r="N29" s="7" t="n"/>
-      <c r="O29" s="7" t="n"/>
+      <c r="B29" s="14" t="n">
+        <v>0.8725000000000001</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>0.8014</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>0.7457</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>0.7435</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>0.8013</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>0.5734</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>0.7083</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>8.575104605663618</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>79.062</v>
+      </c>
+      <c r="M29" s="14" t="n">
+        <v>68.44</v>
+      </c>
+      <c r="N29" s="14" t="n">
+        <v>80.21486026616728</v>
+      </c>
+      <c r="O29" s="14" t="n">
+        <v>78.75421506654182</v>
+      </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
@@ -7674,20 +8143,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="7" t="n"/>
-      <c r="L30" s="7" t="n"/>
-      <c r="M30" s="7" t="n"/>
-      <c r="N30" s="7" t="n"/>
-      <c r="O30" s="7" t="n"/>
+      <c r="B30" s="14" t="n">
+        <v>0.8661</v>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>0.8123</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>0.7171999999999999</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>0.7942</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>0.5589</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>0.6968</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>9.560181010365659</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>84</v>
+      </c>
+      <c r="L30" s="14" t="n">
+        <v>75.652</v>
+      </c>
+      <c r="M30" s="14" t="n">
+        <v>48.64</v>
+      </c>
+      <c r="N30" s="14" t="n">
+        <v>75.7612713100244</v>
+      </c>
+      <c r="O30" s="14" t="n">
+        <v>71.01331782750609</v>
+      </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
@@ -7695,20 +8192,48 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="9" t="n"/>
-      <c r="K31" s="7" t="n"/>
-      <c r="L31" s="7" t="n"/>
-      <c r="M31" s="7" t="n"/>
-      <c r="N31" s="7" t="n"/>
-      <c r="O31" s="7" t="n"/>
+      <c r="B31" s="14" t="n">
+        <v>0.8606</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>0.8123</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>0.6788</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>0.7423999999999999</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>0.4898</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>12.00002940832749</v>
+      </c>
+      <c r="K31" s="14" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="L31" s="14" t="n">
+        <v>71.46000000000001</v>
+      </c>
+      <c r="M31" s="14" t="n">
+        <v>37.96</v>
+      </c>
+      <c r="N31" s="14" t="n">
+        <v>63.78335559738261</v>
+      </c>
+      <c r="O31" s="14" t="n">
+        <v>62.22583889934566</v>
+      </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
@@ -8607,15 +9132,33 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="14" t="n"/>
-      <c r="I14" s="14" t="n"/>
-      <c r="J14" s="14" t="n"/>
+      <c r="B14" s="14" t="n">
+        <v>0.8599</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>0.7171</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>0.6882</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>0.6492</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>9.793435793805299</v>
+      </c>
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
@@ -8799,20 +9342,58 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="14" t="n"/>
-      <c r="H20" s="14" t="n"/>
-      <c r="I20" s="14" t="n"/>
-      <c r="J20" s="14" t="n"/>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
-      <c r="O20" s="8" t="n"/>
+      <c r="B20" s="14" t="n">
+        <v>0.8676</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>0.7544999999999999</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>0.7484</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>0.6803</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>0.8064</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>0.6925</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>9.11681954741025</v>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
@@ -8820,20 +9401,58 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="n"/>
-      <c r="O21" s="7" t="n"/>
+      <c r="B21" s="14" t="n">
+        <v>0.8596</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>0.7509</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>0.7336</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>0.6985</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>0.8081</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>0.5623</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>0.6887</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>9.708701054188552</v>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
@@ -8841,20 +9460,58 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="7" t="n"/>
-      <c r="N22" s="7" t="n"/>
-      <c r="O22" s="7" t="n"/>
+      <c r="B22" s="14" t="n">
+        <v>0.8602</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>0.7726</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>0.7065</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>0.7088</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>0.5341</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>0.6832</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>10.86572566744906</v>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
@@ -8862,20 +9519,58 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
-      <c r="N23" s="7" t="n"/>
-      <c r="O23" s="7" t="n"/>
+      <c r="B23" s="14" t="n">
+        <v>0.8379</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>0.7653</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>0.6533</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>0.6882</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>0.6898</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>0.4625</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>0.6381</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>12.83001820672503</v>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
@@ -11698,20 +12393,48 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
-      <c r="N23" s="7" t="n"/>
-      <c r="O23" s="7" t="n"/>
+      <c r="B23" s="14" t="n">
+        <v>0.5645</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>0.5668</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>0.5059</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>0.2398</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>44.39827896786242</v>
+      </c>
+      <c r="K23" s="14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="14" t="n">
+        <v>3.33</v>
+      </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
@@ -11719,20 +12442,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="7" t="n"/>
-      <c r="N24" s="7" t="n"/>
-      <c r="O24" s="7" t="n"/>
+      <c r="B24" s="14" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>0.5091</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0.2278</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>196.6265942553025</v>
+      </c>
+      <c r="K24" s="14" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="N24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="14" t="n">
+        <v>1.735</v>
+      </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -11740,20 +12491,48 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="7" t="n"/>
-      <c r="L25" s="7" t="n"/>
-      <c r="M25" s="7" t="n"/>
-      <c r="N25" s="7" t="n"/>
-      <c r="O25" s="7" t="n"/>
+      <c r="B25" s="14" t="n">
+        <v>0.4804</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0.4621</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>0.2737</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>0.4886</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.2647</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0.2304</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>3384.194450326494</v>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="14" t="n">
+        <v>0.025</v>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -14284,20 +15063,48 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
-      <c r="N23" s="7" t="n"/>
-      <c r="O23" s="7" t="n"/>
+      <c r="B23" s="14" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>0.5379</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>0.5145999999999999</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>0.2338</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>79.60516653518044</v>
+      </c>
+      <c r="K23" s="14" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="14" t="n">
+        <v>3.175</v>
+      </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
@@ -14305,20 +15112,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="7" t="n"/>
-      <c r="N24" s="7" t="n"/>
-      <c r="O24" s="7" t="n"/>
+      <c r="B24" s="14" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>0.5306999999999999</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0.2321</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>263.2552058939378</v>
+      </c>
+      <c r="K24" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="14" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -14326,20 +15161,48 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="7" t="n"/>
-      <c r="L25" s="7" t="n"/>
-      <c r="M25" s="7" t="n"/>
-      <c r="N25" s="7" t="n"/>
-      <c r="O25" s="7" t="n"/>
+      <c r="B25" s="14" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0.5235</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>0.2579</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>0.4972</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0.2227</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>429.6519329827953</v>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="14" t="n">
+        <v>0.175</v>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -16870,20 +17733,48 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
-      <c r="N23" s="7" t="n"/>
-      <c r="O23" s="7" t="n"/>
+      <c r="B23" s="14" t="n">
+        <v>0.6196</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>0.4946</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>0.5572</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>529.4422774676189</v>
+      </c>
+      <c r="K23" s="14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>8.677999999999999</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N23" s="14" t="n">
+        <v>3.597825703262948</v>
+      </c>
+      <c r="O23" s="14" t="n">
+        <v>6.128956425815738</v>
+      </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
@@ -16891,20 +17782,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="7" t="n"/>
-      <c r="N24" s="7" t="n"/>
-      <c r="O24" s="7" t="n"/>
+      <c r="B24" s="14" t="n">
+        <v>0.6217</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>0.4729</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>0.5004</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>6509.085578872431</v>
+      </c>
+      <c r="K24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="14" t="n">
+        <v>0.08925383791503035</v>
+      </c>
+      <c r="O24" s="14" t="n">
+        <v>0.02231345947875759</v>
+      </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -16912,20 +17831,48 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="7" t="n"/>
-      <c r="L25" s="7" t="n"/>
-      <c r="M25" s="7" t="n"/>
-      <c r="N25" s="7" t="n"/>
-      <c r="O25" s="7" t="n"/>
+      <c r="B25" s="14" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0.4729</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>0.3898</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>33669.07960345771</v>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="14" t="n">
+        <v>0.08925383791503035</v>
+      </c>
+      <c r="O25" s="14" t="n">
+        <v>0.02231345947875759</v>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -18755,15 +19702,33 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="14" t="n"/>
-      <c r="J8" s="14" t="n"/>
+      <c r="B8" s="14" t="n">
+        <v>0.8343</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0.8123</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>0.6237</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0.6535</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>0.6919</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>0.6375</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>15.05541699473268</v>
+      </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -18796,15 +19761,33 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
-      <c r="J9" s="14" t="n"/>
+      <c r="B9" s="14" t="n">
+        <v>0.8505</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>0.7834</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>0.6881</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0.6803</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0.7496</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>0.4846</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0.6661</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>10.17427293285325</v>
+      </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -19197,20 +20180,58 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="14" t="n"/>
-      <c r="H20" s="14" t="n"/>
-      <c r="I20" s="14" t="n"/>
-      <c r="J20" s="14" t="n"/>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
-      <c r="O20" s="8" t="n"/>
+      <c r="B20" s="14" t="n">
+        <v>0.8663999999999999</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>0.7581</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>0.7448</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>0.8102</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0.5555</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>0.6915</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>9.123142806408664</v>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
@@ -19395,15 +20416,33 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="14" t="n"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="14" t="n"/>
-      <c r="H24" s="14" t="n"/>
-      <c r="I24" s="14" t="n"/>
-      <c r="J24" s="14" t="n"/>
+      <c r="B24" s="14" t="n">
+        <v>0.8214</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>0.6101</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>0.5583</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>0.6322</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>0.6961000000000001</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>0.5823</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>15.42049608204206</v>
+      </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -19596,20 +20635,48 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="7" t="n"/>
-      <c r="L29" s="7" t="n"/>
-      <c r="M29" s="7" t="n"/>
-      <c r="N29" s="7" t="n"/>
-      <c r="O29" s="7" t="n"/>
+      <c r="B29" s="14" t="n">
+        <v>0.8771</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>0.7312</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>0.7181999999999999</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>0.7879</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>0.5683</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>8.467775334878283</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>88</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>80.80800000000001</v>
+      </c>
+      <c r="M29" s="14" t="n">
+        <v>77.08</v>
+      </c>
+      <c r="N29" s="14" t="n">
+        <v>80.30591389225862</v>
+      </c>
+      <c r="O29" s="14" t="n">
+        <v>81.54847847306465</v>
+      </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
@@ -19617,20 +20684,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="7" t="n"/>
-      <c r="L30" s="7" t="n"/>
-      <c r="M30" s="7" t="n"/>
-      <c r="N30" s="7" t="n"/>
-      <c r="O30" s="7" t="n"/>
+      <c r="B30" s="14" t="n">
+        <v>0.8639</v>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>0.6804</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>0.6953</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>0.7997</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>0.5495</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>0.6885</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>9.562225659703412</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="L30" s="14" t="n">
+        <v>76.89400000000001</v>
+      </c>
+      <c r="M30" s="14" t="n">
+        <v>56.24</v>
+      </c>
+      <c r="N30" s="14" t="n">
+        <v>75.20974240949471</v>
+      </c>
+      <c r="O30" s="14" t="n">
+        <v>73.31093560237369</v>
+      </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
@@ -19638,20 +20733,48 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="9" t="n"/>
-      <c r="K31" s="7" t="n"/>
-      <c r="L31" s="7" t="n"/>
-      <c r="M31" s="7" t="n"/>
-      <c r="N31" s="7" t="n"/>
-      <c r="O31" s="7" t="n"/>
+      <c r="B31" s="14" t="n">
+        <v>0.8275</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>0.7653</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>0.5703</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>0.6385</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>0.6111</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>14.24243808975662</v>
+      </c>
+      <c r="K31" s="14" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="L31" s="14" t="n">
+        <v>70.61199999999999</v>
+      </c>
+      <c r="M31" s="14" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="N31" s="14" t="n">
+        <v>60.54066935373105</v>
+      </c>
+      <c r="O31" s="14" t="n">
+        <v>64.91316733843276</v>
+      </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="6" t="inlineStr">

--- a/剪枝结果-飞书.xlsx
+++ b/剪枝结果-飞书.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.71928571428571" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
@@ -1939,12 +1939,139 @@
       <c r="N31" s="7" t="n"/>
       <c r="O31" s="7" t="n"/>
     </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>minicpm-v</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="13" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
+      <c r="N33" s="7" t="n"/>
+      <c r="O33" s="7" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="7" t="n"/>
+      <c r="O34" s="7" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
+      <c r="N35" s="7" t="n"/>
+      <c r="O35" s="7" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
+      <c r="N36" s="7" t="n"/>
+      <c r="O36" s="7" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
+      <c r="O37" s="7" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A20:O20"/>
     <mergeCell ref="A26:O26"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A14:O14"/>
+    <mergeCell ref="A32:O32"/>
     <mergeCell ref="A8:O8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1957,7 +2084,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.71928571428571" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
@@ -3466,11 +3593,180 @@
       <c r="N41" s="8" t="n"/>
       <c r="O41" s="8" t="n"/>
     </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>minicpm-v</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="12" t="n"/>
+      <c r="H42" s="12" t="n"/>
+      <c r="I42" s="12" t="n"/>
+      <c r="J42" s="12" t="n"/>
+      <c r="K42" s="12" t="n"/>
+      <c r="L42" s="12" t="n"/>
+      <c r="M42" s="12" t="n"/>
+      <c r="N42" s="12" t="n"/>
+      <c r="O42" s="13" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="7" t="n"/>
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
+      <c r="N43" s="7" t="n"/>
+      <c r="O43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="9" t="n"/>
+      <c r="I44" s="9" t="n"/>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="7" t="n"/>
+      <c r="L44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
+      <c r="N44" s="7" t="n"/>
+      <c r="O44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="7" t="n"/>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
+      <c r="N45" s="7" t="n"/>
+      <c r="O45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+      <c r="I46" s="9" t="n"/>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="7" t="n"/>
+      <c r="L46" s="7" t="n"/>
+      <c r="M46" s="7" t="n"/>
+      <c r="N46" s="7" t="n"/>
+      <c r="O46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
+      <c r="I47" s="9" t="n"/>
+      <c r="J47" s="9" t="n"/>
+      <c r="K47" s="7" t="n"/>
+      <c r="L47" s="7" t="n"/>
+      <c r="M47" s="7" t="n"/>
+      <c r="N47" s="7" t="n"/>
+      <c r="O47" s="7" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="14" t="n"/>
+      <c r="E48" s="14" t="n"/>
+      <c r="F48" s="14" t="n"/>
+      <c r="G48" s="14" t="n"/>
+      <c r="H48" s="14" t="n"/>
+      <c r="I48" s="14" t="n"/>
+      <c r="J48" s="14" t="n"/>
+      <c r="K48" s="8" t="n"/>
+      <c r="L48" s="8" t="n"/>
+      <c r="M48" s="8" t="n"/>
+      <c r="N48" s="8" t="n"/>
+      <c r="O48" s="8" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>4:8</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="14" t="n"/>
+      <c r="E49" s="14" t="n"/>
+      <c r="F49" s="14" t="n"/>
+      <c r="G49" s="14" t="n"/>
+      <c r="H49" s="14" t="n"/>
+      <c r="I49" s="14" t="n"/>
+      <c r="J49" s="14" t="n"/>
+      <c r="K49" s="8" t="n"/>
+      <c r="L49" s="8" t="n"/>
+      <c r="M49" s="8" t="n"/>
+      <c r="N49" s="8" t="n"/>
+      <c r="O49" s="8" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A26:O26"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A42:O42"/>
     <mergeCell ref="A34:O34"/>
     <mergeCell ref="A18:O18"/>
   </mergeCells>
@@ -3484,7 +3780,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.71928571428571" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
@@ -5187,11 +5483,180 @@
       <c r="N41" s="8" t="n"/>
       <c r="O41" s="8" t="n"/>
     </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>minicpm-v</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="12" t="n"/>
+      <c r="H42" s="12" t="n"/>
+      <c r="I42" s="12" t="n"/>
+      <c r="J42" s="12" t="n"/>
+      <c r="K42" s="12" t="n"/>
+      <c r="L42" s="12" t="n"/>
+      <c r="M42" s="12" t="n"/>
+      <c r="N42" s="12" t="n"/>
+      <c r="O42" s="13" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
+      <c r="N43" s="7" t="n"/>
+      <c r="O43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="9" t="n"/>
+      <c r="I44" s="9" t="n"/>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="9" t="n"/>
+      <c r="L44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
+      <c r="N44" s="7" t="n"/>
+      <c r="O44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="9" t="n"/>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
+      <c r="N45" s="7" t="n"/>
+      <c r="O45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+      <c r="I46" s="9" t="n"/>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="9" t="n"/>
+      <c r="L46" s="7" t="n"/>
+      <c r="M46" s="7" t="n"/>
+      <c r="N46" s="7" t="n"/>
+      <c r="O46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
+      <c r="I47" s="9" t="n"/>
+      <c r="J47" s="9" t="n"/>
+      <c r="K47" s="9" t="n"/>
+      <c r="L47" s="7" t="n"/>
+      <c r="M47" s="7" t="n"/>
+      <c r="N47" s="7" t="n"/>
+      <c r="O47" s="7" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="14" t="n"/>
+      <c r="E48" s="14" t="n"/>
+      <c r="F48" s="14" t="n"/>
+      <c r="G48" s="14" t="n"/>
+      <c r="H48" s="14" t="n"/>
+      <c r="I48" s="14" t="n"/>
+      <c r="J48" s="14" t="n"/>
+      <c r="K48" s="8" t="n"/>
+      <c r="L48" s="8" t="n"/>
+      <c r="M48" s="8" t="n"/>
+      <c r="N48" s="8" t="n"/>
+      <c r="O48" s="8" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>4:8</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="14" t="n"/>
+      <c r="E49" s="14" t="n"/>
+      <c r="F49" s="14" t="n"/>
+      <c r="G49" s="14" t="n"/>
+      <c r="H49" s="14" t="n"/>
+      <c r="I49" s="14" t="n"/>
+      <c r="J49" s="14" t="n"/>
+      <c r="K49" s="8" t="n"/>
+      <c r="L49" s="8" t="n"/>
+      <c r="M49" s="8" t="n"/>
+      <c r="N49" s="8" t="n"/>
+      <c r="O49" s="8" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A26:O26"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A42:O42"/>
     <mergeCell ref="A34:O34"/>
     <mergeCell ref="A18:O18"/>
   </mergeCells>
@@ -5205,7 +5670,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.71928571428571" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
@@ -6714,11 +7179,180 @@
       <c r="N41" s="8" t="n"/>
       <c r="O41" s="8" t="n"/>
     </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>minicpm-v</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="12" t="n"/>
+      <c r="H42" s="12" t="n"/>
+      <c r="I42" s="12" t="n"/>
+      <c r="J42" s="12" t="n"/>
+      <c r="K42" s="12" t="n"/>
+      <c r="L42" s="12" t="n"/>
+      <c r="M42" s="12" t="n"/>
+      <c r="N42" s="12" t="n"/>
+      <c r="O42" s="13" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="7" t="n"/>
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
+      <c r="N43" s="7" t="n"/>
+      <c r="O43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="9" t="n"/>
+      <c r="I44" s="9" t="n"/>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="7" t="n"/>
+      <c r="L44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
+      <c r="N44" s="7" t="n"/>
+      <c r="O44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="7" t="n"/>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
+      <c r="N45" s="7" t="n"/>
+      <c r="O45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+      <c r="I46" s="9" t="n"/>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="7" t="n"/>
+      <c r="L46" s="7" t="n"/>
+      <c r="M46" s="7" t="n"/>
+      <c r="N46" s="7" t="n"/>
+      <c r="O46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
+      <c r="I47" s="9" t="n"/>
+      <c r="J47" s="9" t="n"/>
+      <c r="K47" s="7" t="n"/>
+      <c r="L47" s="7" t="n"/>
+      <c r="M47" s="7" t="n"/>
+      <c r="N47" s="7" t="n"/>
+      <c r="O47" s="7" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="14" t="n"/>
+      <c r="E48" s="14" t="n"/>
+      <c r="F48" s="14" t="n"/>
+      <c r="G48" s="14" t="n"/>
+      <c r="H48" s="14" t="n"/>
+      <c r="I48" s="14" t="n"/>
+      <c r="J48" s="14" t="n"/>
+      <c r="K48" s="8" t="n"/>
+      <c r="L48" s="8" t="n"/>
+      <c r="M48" s="8" t="n"/>
+      <c r="N48" s="8" t="n"/>
+      <c r="O48" s="8" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>4:8</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="14" t="n"/>
+      <c r="E49" s="14" t="n"/>
+      <c r="F49" s="14" t="n"/>
+      <c r="G49" s="14" t="n"/>
+      <c r="H49" s="14" t="n"/>
+      <c r="I49" s="14" t="n"/>
+      <c r="J49" s="14" t="n"/>
+      <c r="K49" s="8" t="n"/>
+      <c r="L49" s="8" t="n"/>
+      <c r="M49" s="8" t="n"/>
+      <c r="N49" s="8" t="n"/>
+      <c r="O49" s="8" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A26:O26"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A42:O42"/>
     <mergeCell ref="A34:O34"/>
     <mergeCell ref="A18:O18"/>
   </mergeCells>
@@ -6732,7 +7366,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.71928571428571" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
@@ -8445,11 +9079,180 @@
       <c r="N41" s="8" t="n"/>
       <c r="O41" s="8" t="n"/>
     </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>minicpm-v</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="12" t="n"/>
+      <c r="H42" s="12" t="n"/>
+      <c r="I42" s="12" t="n"/>
+      <c r="J42" s="12" t="n"/>
+      <c r="K42" s="12" t="n"/>
+      <c r="L42" s="12" t="n"/>
+      <c r="M42" s="12" t="n"/>
+      <c r="N42" s="12" t="n"/>
+      <c r="O42" s="13" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="7" t="n"/>
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
+      <c r="N43" s="7" t="n"/>
+      <c r="O43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="9" t="n"/>
+      <c r="I44" s="9" t="n"/>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="7" t="n"/>
+      <c r="L44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
+      <c r="N44" s="7" t="n"/>
+      <c r="O44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="7" t="n"/>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
+      <c r="N45" s="7" t="n"/>
+      <c r="O45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+      <c r="I46" s="9" t="n"/>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="7" t="n"/>
+      <c r="L46" s="7" t="n"/>
+      <c r="M46" s="7" t="n"/>
+      <c r="N46" s="7" t="n"/>
+      <c r="O46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
+      <c r="I47" s="9" t="n"/>
+      <c r="J47" s="9" t="n"/>
+      <c r="K47" s="7" t="n"/>
+      <c r="L47" s="7" t="n"/>
+      <c r="M47" s="7" t="n"/>
+      <c r="N47" s="7" t="n"/>
+      <c r="O47" s="7" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="14" t="n"/>
+      <c r="E48" s="14" t="n"/>
+      <c r="F48" s="14" t="n"/>
+      <c r="G48" s="14" t="n"/>
+      <c r="H48" s="14" t="n"/>
+      <c r="I48" s="14" t="n"/>
+      <c r="J48" s="14" t="n"/>
+      <c r="K48" s="8" t="n"/>
+      <c r="L48" s="8" t="n"/>
+      <c r="M48" s="8" t="n"/>
+      <c r="N48" s="8" t="n"/>
+      <c r="O48" s="8" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>4:8</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="14" t="n"/>
+      <c r="E49" s="14" t="n"/>
+      <c r="F49" s="14" t="n"/>
+      <c r="G49" s="14" t="n"/>
+      <c r="H49" s="14" t="n"/>
+      <c r="I49" s="14" t="n"/>
+      <c r="J49" s="14" t="n"/>
+      <c r="K49" s="8" t="n"/>
+      <c r="L49" s="8" t="n"/>
+      <c r="M49" s="8" t="n"/>
+      <c r="N49" s="8" t="n"/>
+      <c r="O49" s="8" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A26:O26"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A42:O42"/>
     <mergeCell ref="A34:O34"/>
     <mergeCell ref="A18:O18"/>
   </mergeCells>
@@ -8463,7 +9266,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.71928571428571" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
@@ -9990,11 +10793,180 @@
       <c r="N41" s="8" t="n"/>
       <c r="O41" s="8" t="n"/>
     </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>minicpm-v</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="12" t="n"/>
+      <c r="H42" s="12" t="n"/>
+      <c r="I42" s="12" t="n"/>
+      <c r="J42" s="12" t="n"/>
+      <c r="K42" s="12" t="n"/>
+      <c r="L42" s="12" t="n"/>
+      <c r="M42" s="12" t="n"/>
+      <c r="N42" s="12" t="n"/>
+      <c r="O42" s="13" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="7" t="n"/>
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
+      <c r="N43" s="7" t="n"/>
+      <c r="O43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="9" t="n"/>
+      <c r="I44" s="9" t="n"/>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="7" t="n"/>
+      <c r="L44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
+      <c r="N44" s="7" t="n"/>
+      <c r="O44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="7" t="n"/>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
+      <c r="N45" s="7" t="n"/>
+      <c r="O45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+      <c r="I46" s="9" t="n"/>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="7" t="n"/>
+      <c r="L46" s="7" t="n"/>
+      <c r="M46" s="7" t="n"/>
+      <c r="N46" s="7" t="n"/>
+      <c r="O46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
+      <c r="I47" s="9" t="n"/>
+      <c r="J47" s="9" t="n"/>
+      <c r="K47" s="7" t="n"/>
+      <c r="L47" s="7" t="n"/>
+      <c r="M47" s="7" t="n"/>
+      <c r="N47" s="7" t="n"/>
+      <c r="O47" s="7" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="14" t="n"/>
+      <c r="E48" s="14" t="n"/>
+      <c r="F48" s="14" t="n"/>
+      <c r="G48" s="14" t="n"/>
+      <c r="H48" s="14" t="n"/>
+      <c r="I48" s="14" t="n"/>
+      <c r="J48" s="14" t="n"/>
+      <c r="K48" s="8" t="n"/>
+      <c r="L48" s="8" t="n"/>
+      <c r="M48" s="8" t="n"/>
+      <c r="N48" s="8" t="n"/>
+      <c r="O48" s="8" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>4:8</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="14" t="n"/>
+      <c r="E49" s="14" t="n"/>
+      <c r="F49" s="14" t="n"/>
+      <c r="G49" s="14" t="n"/>
+      <c r="H49" s="14" t="n"/>
+      <c r="I49" s="14" t="n"/>
+      <c r="J49" s="14" t="n"/>
+      <c r="K49" s="8" t="n"/>
+      <c r="L49" s="8" t="n"/>
+      <c r="M49" s="8" t="n"/>
+      <c r="N49" s="8" t="n"/>
+      <c r="O49" s="8" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A26:O26"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A42:O42"/>
     <mergeCell ref="A34:O34"/>
     <mergeCell ref="A18:O18"/>
   </mergeCells>
@@ -10008,7 +10980,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.71928571428571" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
@@ -11255,12 +12227,139 @@
       <c r="N31" s="7" t="n"/>
       <c r="O31" s="7" t="n"/>
     </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>minicpm-v</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="13" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
+      <c r="N33" s="7" t="n"/>
+      <c r="O33" s="7" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="7" t="n"/>
+      <c r="O34" s="7" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
+      <c r="N35" s="7" t="n"/>
+      <c r="O35" s="7" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
+      <c r="N36" s="7" t="n"/>
+      <c r="O36" s="7" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
+      <c r="O37" s="7" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A20:O20"/>
     <mergeCell ref="A26:O26"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A14:O14"/>
+    <mergeCell ref="A32:O32"/>
     <mergeCell ref="A8:O8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11273,7 +12372,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.71928571428571" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
@@ -12660,12 +13759,139 @@
       <c r="N31" s="7" t="n"/>
       <c r="O31" s="7" t="n"/>
     </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>minicpm-v</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="13" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
+      <c r="N33" s="7" t="n"/>
+      <c r="O33" s="7" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="7" t="n"/>
+      <c r="O34" s="7" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
+      <c r="N35" s="7" t="n"/>
+      <c r="O35" s="7" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
+      <c r="N36" s="7" t="n"/>
+      <c r="O36" s="7" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
+      <c r="O37" s="7" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A20:O20"/>
     <mergeCell ref="A26:O26"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A14:O14"/>
+    <mergeCell ref="A32:O32"/>
     <mergeCell ref="A8:O8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12678,7 +13904,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.71928571428571" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
@@ -13925,12 +15151,139 @@
       <c r="N31" s="7" t="n"/>
       <c r="O31" s="7" t="n"/>
     </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>minicpm-v</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="13" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
+      <c r="N33" s="7" t="n"/>
+      <c r="O33" s="7" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="7" t="n"/>
+      <c r="O34" s="7" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
+      <c r="N35" s="7" t="n"/>
+      <c r="O35" s="7" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
+      <c r="N36" s="7" t="n"/>
+      <c r="O36" s="7" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
+      <c r="O37" s="7" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A20:O20"/>
     <mergeCell ref="A26:O26"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A14:O14"/>
+    <mergeCell ref="A32:O32"/>
     <mergeCell ref="A8:O8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13943,7 +15296,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.71928571428571" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
@@ -15330,12 +16683,139 @@
       <c r="N31" s="7" t="n"/>
       <c r="O31" s="7" t="n"/>
     </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>minicpm-v</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="13" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
+      <c r="N33" s="7" t="n"/>
+      <c r="O33" s="7" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="7" t="n"/>
+      <c r="O34" s="7" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
+      <c r="N35" s="7" t="n"/>
+      <c r="O35" s="7" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
+      <c r="N36" s="7" t="n"/>
+      <c r="O36" s="7" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
+      <c r="O37" s="7" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A20:O20"/>
     <mergeCell ref="A26:O26"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A14:O14"/>
+    <mergeCell ref="A32:O32"/>
     <mergeCell ref="A8:O8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15348,7 +16828,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.71928571428571" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
@@ -16595,12 +18075,139 @@
       <c r="N31" s="7" t="n"/>
       <c r="O31" s="7" t="n"/>
     </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>minicpm-v</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="13" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
+      <c r="N33" s="7" t="n"/>
+      <c r="O33" s="7" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="7" t="n"/>
+      <c r="O34" s="7" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
+      <c r="N35" s="7" t="n"/>
+      <c r="O35" s="7" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
+      <c r="N36" s="7" t="n"/>
+      <c r="O36" s="7" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
+      <c r="O37" s="7" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A20:O20"/>
     <mergeCell ref="A26:O26"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A14:O14"/>
+    <mergeCell ref="A32:O32"/>
     <mergeCell ref="A8:O8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16613,7 +18220,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.71928571428571" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
@@ -18000,12 +19607,139 @@
       <c r="N31" s="7" t="n"/>
       <c r="O31" s="7" t="n"/>
     </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>minicpm-v</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="13" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
+      <c r="N33" s="7" t="n"/>
+      <c r="O33" s="7" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="7" t="n"/>
+      <c r="O34" s="7" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
+      <c r="N35" s="7" t="n"/>
+      <c r="O35" s="7" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
+      <c r="N36" s="7" t="n"/>
+      <c r="O36" s="7" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
+      <c r="O37" s="7" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A20:O20"/>
     <mergeCell ref="A26:O26"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A14:O14"/>
+    <mergeCell ref="A32:O32"/>
     <mergeCell ref="A8:O8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18018,7 +19752,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.71928571428571" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
@@ -19265,12 +20999,139 @@
       <c r="N31" s="7" t="n"/>
       <c r="O31" s="7" t="n"/>
     </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>minicpm-v</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="13" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
+      <c r="N33" s="7" t="n"/>
+      <c r="O33" s="7" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="7" t="n"/>
+      <c r="O34" s="7" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
+      <c r="N35" s="7" t="n"/>
+      <c r="O35" s="7" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
+      <c r="N36" s="7" t="n"/>
+      <c r="O36" s="7" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
+      <c r="O37" s="7" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A20:O20"/>
     <mergeCell ref="A26:O26"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A14:O14"/>
+    <mergeCell ref="A32:O32"/>
     <mergeCell ref="A8:O8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19283,7 +21144,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.71928571428571" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
@@ -20986,11 +22847,180 @@
       <c r="N41" s="8" t="n"/>
       <c r="O41" s="8" t="n"/>
     </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>minicpm-v</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="12" t="n"/>
+      <c r="H42" s="12" t="n"/>
+      <c r="I42" s="12" t="n"/>
+      <c r="J42" s="12" t="n"/>
+      <c r="K42" s="12" t="n"/>
+      <c r="L42" s="12" t="n"/>
+      <c r="M42" s="12" t="n"/>
+      <c r="N42" s="12" t="n"/>
+      <c r="O42" s="13" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="7" t="n"/>
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
+      <c r="N43" s="7" t="n"/>
+      <c r="O43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="9" t="n"/>
+      <c r="I44" s="9" t="n"/>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="7" t="n"/>
+      <c r="L44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
+      <c r="N44" s="7" t="n"/>
+      <c r="O44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="7" t="n"/>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
+      <c r="N45" s="7" t="n"/>
+      <c r="O45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+      <c r="I46" s="9" t="n"/>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="7" t="n"/>
+      <c r="L46" s="7" t="n"/>
+      <c r="M46" s="7" t="n"/>
+      <c r="N46" s="7" t="n"/>
+      <c r="O46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
+      <c r="I47" s="9" t="n"/>
+      <c r="J47" s="9" t="n"/>
+      <c r="K47" s="7" t="n"/>
+      <c r="L47" s="7" t="n"/>
+      <c r="M47" s="7" t="n"/>
+      <c r="N47" s="7" t="n"/>
+      <c r="O47" s="7" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="14" t="n"/>
+      <c r="E48" s="14" t="n"/>
+      <c r="F48" s="14" t="n"/>
+      <c r="G48" s="14" t="n"/>
+      <c r="H48" s="14" t="n"/>
+      <c r="I48" s="14" t="n"/>
+      <c r="J48" s="14" t="n"/>
+      <c r="K48" s="8" t="n"/>
+      <c r="L48" s="8" t="n"/>
+      <c r="M48" s="8" t="n"/>
+      <c r="N48" s="8" t="n"/>
+      <c r="O48" s="8" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>4:8</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="14" t="n"/>
+      <c r="E49" s="14" t="n"/>
+      <c r="F49" s="14" t="n"/>
+      <c r="G49" s="14" t="n"/>
+      <c r="H49" s="14" t="n"/>
+      <c r="I49" s="14" t="n"/>
+      <c r="J49" s="14" t="n"/>
+      <c r="K49" s="8" t="n"/>
+      <c r="L49" s="8" t="n"/>
+      <c r="M49" s="8" t="n"/>
+      <c r="N49" s="8" t="n"/>
+      <c r="O49" s="8" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A26:O26"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A42:O42"/>
     <mergeCell ref="A34:O34"/>
     <mergeCell ref="A18:O18"/>
   </mergeCells>

--- a/剪枝结果-飞书.xlsx
+++ b/剪枝结果-飞书.xlsx
@@ -1966,20 +1966,48 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="7" t="n"/>
-      <c r="L33" s="7" t="n"/>
-      <c r="M33" s="7" t="n"/>
-      <c r="N33" s="7" t="n"/>
-      <c r="O33" s="7" t="n"/>
+      <c r="B33" s="14" t="n">
+        <v>0.8046</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>0.6956</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>0.6709000000000001</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>0.7445000000000001</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>0.4488</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>0.6441</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>7.553345573106815</v>
+      </c>
+      <c r="K33" s="14" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="L33" s="14" t="n">
+        <v>56.742</v>
+      </c>
+      <c r="M33" s="14" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="N33" s="14" t="n">
+        <v>19.43151262672127</v>
+      </c>
+      <c r="O33" s="14" t="n">
+        <v>39.60837815668032</v>
+      </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
@@ -1987,20 +2015,48 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n"/>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="9" t="n"/>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="9" t="n"/>
-      <c r="I34" s="9" t="n"/>
-      <c r="J34" s="9" t="n"/>
-      <c r="K34" s="7" t="n"/>
-      <c r="L34" s="7" t="n"/>
-      <c r="M34" s="7" t="n"/>
-      <c r="N34" s="7" t="n"/>
-      <c r="O34" s="7" t="n"/>
+      <c r="B34" s="14" t="n">
+        <v>0.6269</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>0.5451</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>0.6021</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>0.6433</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>0.6604</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <v>0.5531</v>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>9.174124058963613</v>
+      </c>
+      <c r="K34" s="14" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="L34" s="14" t="n">
+        <v>50.02</v>
+      </c>
+      <c r="M34" s="14" t="n">
+        <v>39.24</v>
+      </c>
+      <c r="N34" s="14" t="n">
+        <v>17.09025819112553</v>
+      </c>
+      <c r="O34" s="14" t="n">
+        <v>34.78756454778138</v>
+      </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
@@ -2008,20 +2064,48 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="7" t="n"/>
-      <c r="L35" s="7" t="n"/>
-      <c r="M35" s="7" t="n"/>
-      <c r="N35" s="7" t="n"/>
-      <c r="O35" s="7" t="n"/>
+      <c r="B35" s="14" t="n">
+        <v>0.6223</v>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>0.5722</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="G35" s="14" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="I35" s="14" t="n">
+        <v>0.4742</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>16.78349021495482</v>
+      </c>
+      <c r="K35" s="14" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L35" s="14" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="M35" s="14" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="N35" s="14" t="n">
+        <v>8.448772901271068</v>
+      </c>
+      <c r="O35" s="14" t="n">
+        <v>14.78469322531777</v>
+      </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
@@ -2029,20 +2113,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="9" t="n"/>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="7" t="n"/>
-      <c r="L36" s="7" t="n"/>
-      <c r="M36" s="7" t="n"/>
-      <c r="N36" s="7" t="n"/>
-      <c r="O36" s="7" t="n"/>
+      <c r="B36" s="14" t="n">
+        <v>0.6187</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>0.5304</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>0.2449</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="I36" s="14" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="J36" s="14" t="n">
+        <v>28.64081228910323</v>
+      </c>
+      <c r="K36" s="14" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="L36" s="14" t="n">
+        <v>8.027999999999999</v>
+      </c>
+      <c r="M36" s="14" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="N36" s="14" t="n">
+        <v>0.5896703558253005</v>
+      </c>
+      <c r="O36" s="14" t="n">
+        <v>4.559417588956324</v>
+      </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
@@ -2050,20 +2162,48 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="7" t="n"/>
-      <c r="L37" s="7" t="n"/>
-      <c r="M37" s="7" t="n"/>
-      <c r="N37" s="7" t="n"/>
-      <c r="O37" s="7" t="n"/>
+      <c r="B37" s="14" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="G37" s="14" t="n">
+        <v>0.2338</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>634.2558491607684</v>
+      </c>
+      <c r="K37" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="14" t="n">
+        <v>1.05</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2753,15 +2893,33 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="14" t="n"/>
-      <c r="I14" s="14" t="n"/>
-      <c r="J14" s="14" t="n"/>
+      <c r="B14" s="14" t="n">
+        <v>0.8566</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>0.7942</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>0.6954</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>0.6772</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>0.6726</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>9.857977828286456</v>
+      </c>
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
@@ -2823,15 +2981,33 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="14" t="n"/>
-      <c r="I16" s="14" t="n"/>
-      <c r="J16" s="14" t="n"/>
+      <c r="B16" s="14" t="n">
+        <v>0.7792</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>0.8014</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>0.5845</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>0.6243</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>0.5631</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>21.4543478127974</v>
+      </c>
       <c r="K16" s="8" t="n"/>
       <c r="L16" s="8" t="n"/>
       <c r="M16" s="8" t="n"/>
@@ -2844,15 +3020,33 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-      <c r="H17" s="14" t="n"/>
-      <c r="I17" s="14" t="n"/>
-      <c r="J17" s="14" t="n"/>
+      <c r="B17" s="14" t="n">
+        <v>0.8290999999999999</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>0.7978</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>0.6504</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>0.6598000000000001</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>0.6103</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>11.94241601793689</v>
+      </c>
       <c r="K17" s="8" t="n"/>
       <c r="L17" s="8" t="n"/>
       <c r="M17" s="8" t="n"/>
@@ -3284,15 +3478,33 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
+      <c r="B27" s="14" t="n">
+        <v>0.8749</v>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>0.7645</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>0.7364000000000001</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>0.8232</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>0.6109</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>0.7193000000000001</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>7.855145447281187</v>
+      </c>
       <c r="K27" s="7" t="n"/>
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
@@ -3305,20 +3517,38 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
-      <c r="G28" s="9" t="n"/>
-      <c r="H28" s="9" t="n"/>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="7" t="n"/>
-      <c r="L28" s="7" t="n"/>
-      <c r="M28" s="7" t="n"/>
-      <c r="N28" s="7" t="n"/>
-      <c r="O28" s="7" t="n"/>
+      <c r="B28" s="14" t="n">
+        <v>0.8777</v>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>0.7906</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>0.7639</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>0.7332</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>0.8283</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>0.6067</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>0.7195</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>7.898124099315785</v>
+      </c>
+      <c r="K28" s="8" t="n"/>
+      <c r="L28" s="8" t="n"/>
+      <c r="M28" s="8" t="n"/>
+      <c r="N28" s="8" t="n"/>
+      <c r="O28" s="8" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
@@ -3326,15 +3556,33 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
+      <c r="B29" s="14" t="n">
+        <v>0.8749</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>0.8014</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>0.7304</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>0.7252999999999999</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>0.7907999999999999</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>0.5683</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>0.7002</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>8.465834660023512</v>
+      </c>
       <c r="K29" s="7" t="n"/>
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
@@ -3347,15 +3595,33 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="9" t="n"/>
+      <c r="B30" s="14" t="n">
+        <v>0.8653999999999999</v>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>0.8339</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>0.6805</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>0.6922</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>0.8013</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>0.5452</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>0.6881</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>9.55528035790692</v>
+      </c>
       <c r="K30" s="7" t="n"/>
       <c r="L30" s="7" t="n"/>
       <c r="M30" s="7" t="n"/>
@@ -3368,15 +3634,33 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="9" t="n"/>
+      <c r="B31" s="14" t="n">
+        <v>0.8266</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>0.7581</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>0.5695</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>0.6409</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>0.7016</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>0.6085</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>14.2537818262333</v>
+      </c>
       <c r="K31" s="7" t="n"/>
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
@@ -4485,20 +4769,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="14" t="n"/>
-      <c r="I14" s="14" t="n"/>
-      <c r="J14" s="14" t="n"/>
-      <c r="K14" s="8" t="n"/>
-      <c r="L14" s="8" t="n"/>
-      <c r="M14" s="8" t="n"/>
-      <c r="N14" s="8" t="n"/>
-      <c r="O14" s="8" t="n"/>
+      <c r="B14" s="14" t="n">
+        <v>0.8621</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>0.8159</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>0.7079</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>0.6334</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>0.6466</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>9.735336288269114</v>
+      </c>
+      <c r="K14" s="15" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>78.43600000000001</v>
+      </c>
+      <c r="M14" s="15" t="n">
+        <v>66.67999999999999</v>
+      </c>
+      <c r="N14" s="15" t="n">
+        <v>75.62547266865545</v>
+      </c>
+      <c r="O14" s="15" t="n">
+        <v>76.03536816716387</v>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
@@ -4555,20 +4867,48 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="14" t="n"/>
-      <c r="I16" s="14" t="n"/>
-      <c r="J16" s="14" t="n"/>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="8" t="n"/>
-      <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n"/>
-      <c r="O16" s="8" t="n"/>
+      <c r="B16" s="14" t="n">
+        <v>0.7939000000000001</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>0.6107</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>0.6488</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>0.5972</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>0.5962</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>13.5992441035578</v>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="L16" s="15" t="n">
+        <v>78.148</v>
+      </c>
+      <c r="M16" s="15" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="N16" s="15" t="n">
+        <v>70.73909838016162</v>
+      </c>
+      <c r="O16" s="15" t="n">
+        <v>68.8317745950404</v>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -4576,20 +4916,48 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-      <c r="H17" s="14" t="n"/>
-      <c r="I17" s="14" t="n"/>
-      <c r="J17" s="14" t="n"/>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="8" t="n"/>
-      <c r="M17" s="8" t="n"/>
-      <c r="N17" s="8" t="n"/>
-      <c r="O17" s="8" t="n"/>
+      <c r="B17" s="14" t="n">
+        <v>0.8547</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>0.7978</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>0.6613</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>0.6654</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>0.6566</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>11.16547215033378</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>76.67399999999999</v>
+      </c>
+      <c r="M17" s="15" t="n">
+        <v>41.72</v>
+      </c>
+      <c r="N17" s="15" t="n">
+        <v>73.99566217763295</v>
+      </c>
+      <c r="O17" s="15" t="n">
+        <v>68.27241554440823</v>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -4972,15 +5340,33 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="14" t="n"/>
-      <c r="E25" s="14" t="n"/>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="14" t="n"/>
-      <c r="H25" s="14" t="n"/>
-      <c r="I25" s="14" t="n"/>
-      <c r="J25" s="14" t="n"/>
+      <c r="B25" s="14" t="n">
+        <v>0.8486</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0.6606</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>0.6462</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.7647</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0.4872</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>0.6404</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>12.03914646789688</v>
+      </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5279,20 +5665,48 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="14" t="n"/>
-      <c r="E32" s="14" t="n"/>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="14" t="n"/>
-      <c r="H32" s="14" t="n"/>
-      <c r="I32" s="14" t="n"/>
-      <c r="J32" s="14" t="n"/>
-      <c r="K32" s="8" t="n"/>
-      <c r="L32" s="8" t="n"/>
-      <c r="M32" s="8" t="n"/>
-      <c r="N32" s="8" t="n"/>
-      <c r="O32" s="8" t="n"/>
+      <c r="B32" s="14" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>0.7653</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>0.6011</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>0.6646</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>0.7332</v>
+      </c>
+      <c r="G32" s="14" t="n">
+        <v>0.4659</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="I32" s="14" t="n">
+        <v>0.6383</v>
+      </c>
+      <c r="J32" s="14" t="n">
+        <v>13.41084535009583</v>
+      </c>
+      <c r="K32" s="15" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="L32" s="15" t="n">
+        <v>72.988</v>
+      </c>
+      <c r="M32" s="15" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="N32" s="15" t="n">
+        <v>63.60305032003411</v>
+      </c>
+      <c r="O32" s="15" t="n">
+        <v>63.25276258000853</v>
+      </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
@@ -5300,20 +5714,48 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n"/>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="14" t="n"/>
-      <c r="E33" s="14" t="n"/>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="14" t="n"/>
-      <c r="H33" s="14" t="n"/>
-      <c r="I33" s="14" t="n"/>
-      <c r="J33" s="14" t="n"/>
-      <c r="K33" s="8" t="n"/>
-      <c r="L33" s="8" t="n"/>
-      <c r="M33" s="8" t="n"/>
-      <c r="N33" s="8" t="n"/>
-      <c r="O33" s="8" t="n"/>
+      <c r="B33" s="14" t="n">
+        <v>0.8663999999999999</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>0.7653</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>0.6583</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>0.6867</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>0.7588</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>0.5051</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>0.6644</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>11.27526685972145</v>
+      </c>
+      <c r="K33" s="15" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="L33" s="15" t="n">
+        <v>74.39</v>
+      </c>
+      <c r="M33" s="15" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="N33" s="15" t="n">
+        <v>70.33920790328537</v>
+      </c>
+      <c r="O33" s="15" t="n">
+        <v>67.88230197582135</v>
+      </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
@@ -5510,20 +5952,48 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n"/>
-      <c r="C43" s="9" t="n"/>
-      <c r="D43" s="9" t="n"/>
-      <c r="E43" s="9" t="n"/>
-      <c r="F43" s="9" t="n"/>
-      <c r="G43" s="9" t="n"/>
-      <c r="H43" s="9" t="n"/>
-      <c r="I43" s="9" t="n"/>
-      <c r="J43" s="9" t="n"/>
-      <c r="K43" s="9" t="n"/>
-      <c r="L43" s="7" t="n"/>
-      <c r="M43" s="7" t="n"/>
-      <c r="N43" s="7" t="n"/>
-      <c r="O43" s="7" t="n"/>
+      <c r="B43" s="14" t="n">
+        <v>0.8046</v>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>0.6956</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>0.6709000000000001</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>0.7445000000000001</v>
+      </c>
+      <c r="G43" s="14" t="n">
+        <v>0.4488</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I43" s="14" t="n">
+        <v>0.6441</v>
+      </c>
+      <c r="J43" s="14" t="n">
+        <v>7.553345573106815</v>
+      </c>
+      <c r="K43" s="14" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="L43" s="14" t="n">
+        <v>56.742</v>
+      </c>
+      <c r="M43" s="14" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="N43" s="14" t="n">
+        <v>19.43151262672127</v>
+      </c>
+      <c r="O43" s="14" t="n">
+        <v>39.60837815668032</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -5531,20 +6001,48 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n"/>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="9" t="n"/>
-      <c r="E44" s="9" t="n"/>
-      <c r="F44" s="9" t="n"/>
-      <c r="G44" s="9" t="n"/>
-      <c r="H44" s="9" t="n"/>
-      <c r="I44" s="9" t="n"/>
-      <c r="J44" s="9" t="n"/>
-      <c r="K44" s="9" t="n"/>
-      <c r="L44" s="7" t="n"/>
-      <c r="M44" s="7" t="n"/>
-      <c r="N44" s="7" t="n"/>
-      <c r="O44" s="7" t="n"/>
+      <c r="B44" s="14" t="n">
+        <v>0.8034</v>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>0.6606</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>0.6929</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>0.7361</v>
+      </c>
+      <c r="G44" s="14" t="n">
+        <v>0.4462</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="I44" s="14" t="n">
+        <v>0.6359</v>
+      </c>
+      <c r="J44" s="14" t="n">
+        <v>7.642282540815029</v>
+      </c>
+      <c r="K44" s="14" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="L44" s="14" t="n">
+        <v>56.33000000000001</v>
+      </c>
+      <c r="M44" s="14" t="n">
+        <v>44.68</v>
+      </c>
+      <c r="N44" s="14" t="n">
+        <v>19.31309960986033</v>
+      </c>
+      <c r="O44" s="14" t="n">
+        <v>39.13077490246508</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -5552,20 +6050,48 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B45" s="9" t="n"/>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="9" t="n"/>
-      <c r="F45" s="9" t="n"/>
-      <c r="G45" s="9" t="n"/>
-      <c r="H45" s="9" t="n"/>
-      <c r="I45" s="9" t="n"/>
-      <c r="J45" s="9" t="n"/>
-      <c r="K45" s="9" t="n"/>
-      <c r="L45" s="7" t="n"/>
-      <c r="M45" s="7" t="n"/>
-      <c r="N45" s="7" t="n"/>
-      <c r="O45" s="7" t="n"/>
+      <c r="B45" s="14" t="n">
+        <v>0.7697000000000001</v>
+      </c>
+      <c r="C45" s="14" t="n">
+        <v>0.5957</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>0.6754</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>0.7066</v>
+      </c>
+      <c r="G45" s="14" t="n">
+        <v>0.4215</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="I45" s="14" t="n">
+        <v>0.6094000000000001</v>
+      </c>
+      <c r="J45" s="14" t="n">
+        <v>8.213187067414758</v>
+      </c>
+      <c r="K45" s="14" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="L45" s="14" t="n">
+        <v>56.01199999999999</v>
+      </c>
+      <c r="M45" s="14" t="n">
+        <v>43.88</v>
+      </c>
+      <c r="N45" s="14" t="n">
+        <v>17.6076813814649</v>
+      </c>
+      <c r="O45" s="14" t="n">
+        <v>38.29992034536622</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -5573,20 +6099,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B46" s="9" t="n"/>
-      <c r="C46" s="9" t="n"/>
-      <c r="D46" s="9" t="n"/>
-      <c r="E46" s="9" t="n"/>
-      <c r="F46" s="9" t="n"/>
-      <c r="G46" s="9" t="n"/>
-      <c r="H46" s="9" t="n"/>
-      <c r="I46" s="9" t="n"/>
-      <c r="J46" s="9" t="n"/>
-      <c r="K46" s="9" t="n"/>
-      <c r="L46" s="7" t="n"/>
-      <c r="M46" s="7" t="n"/>
-      <c r="N46" s="7" t="n"/>
-      <c r="O46" s="7" t="n"/>
+      <c r="B46" s="14" t="n">
+        <v>0.7401</v>
+      </c>
+      <c r="C46" s="14" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>0.6414</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>0.6575</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>0.6675</v>
+      </c>
+      <c r="G46" s="14" t="n">
+        <v>0.3976</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="I46" s="14" t="n">
+        <v>0.5834</v>
+      </c>
+      <c r="J46" s="14" t="n">
+        <v>9.232294985503087</v>
+      </c>
+      <c r="K46" s="14" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="L46" s="14" t="n">
+        <v>53.09199999999999</v>
+      </c>
+      <c r="M46" s="14" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="N46" s="14" t="n">
+        <v>16.07571961166652</v>
+      </c>
+      <c r="O46" s="14" t="n">
+        <v>35.79192990291663</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -5594,20 +6148,48 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B47" s="9" t="n"/>
-      <c r="C47" s="9" t="n"/>
-      <c r="D47" s="9" t="n"/>
-      <c r="E47" s="9" t="n"/>
-      <c r="F47" s="9" t="n"/>
-      <c r="G47" s="9" t="n"/>
-      <c r="H47" s="9" t="n"/>
-      <c r="I47" s="9" t="n"/>
-      <c r="J47" s="9" t="n"/>
-      <c r="K47" s="9" t="n"/>
-      <c r="L47" s="7" t="n"/>
-      <c r="M47" s="7" t="n"/>
-      <c r="N47" s="7" t="n"/>
-      <c r="O47" s="7" t="n"/>
+      <c r="B47" s="14" t="n">
+        <v>0.7012</v>
+      </c>
+      <c r="C47" s="14" t="n">
+        <v>0.6173</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>0.5743</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>0.6204</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>0.5964</v>
+      </c>
+      <c r="G47" s="14" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I47" s="14" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="J47" s="14" t="n">
+        <v>12.16527777033099</v>
+      </c>
+      <c r="K47" s="14" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="L47" s="14" t="n">
+        <v>45.278</v>
+      </c>
+      <c r="M47" s="14" t="n">
+        <v>36.52</v>
+      </c>
+      <c r="N47" s="14" t="n">
+        <v>14.24474975617425</v>
+      </c>
+      <c r="O47" s="14" t="n">
+        <v>31.63568743904356</v>
+      </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
@@ -5615,20 +6197,48 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B48" s="14" t="n"/>
-      <c r="C48" s="14" t="n"/>
-      <c r="D48" s="14" t="n"/>
-      <c r="E48" s="14" t="n"/>
-      <c r="F48" s="14" t="n"/>
-      <c r="G48" s="14" t="n"/>
-      <c r="H48" s="14" t="n"/>
-      <c r="I48" s="14" t="n"/>
-      <c r="J48" s="14" t="n"/>
-      <c r="K48" s="8" t="n"/>
-      <c r="L48" s="8" t="n"/>
-      <c r="M48" s="8" t="n"/>
-      <c r="N48" s="8" t="n"/>
-      <c r="O48" s="8" t="n"/>
+      <c r="B48" s="14" t="n">
+        <v>0.6235000000000001</v>
+      </c>
+      <c r="C48" s="14" t="n">
+        <v>0.6498</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>0.5499000000000001</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>0.5864</v>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>0.6132</v>
+      </c>
+      <c r="G48" s="14" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="I48" s="14" t="n">
+        <v>0.5296</v>
+      </c>
+      <c r="J48" s="14" t="n">
+        <v>12.47463062182757</v>
+      </c>
+      <c r="K48" s="15" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="L48" s="15" t="n">
+        <v>47.69</v>
+      </c>
+      <c r="M48" s="15" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="N48" s="15" t="n">
+        <v>15.74422021710239</v>
+      </c>
+      <c r="O48" s="15" t="n">
+        <v>33.0935550542756</v>
+      </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
@@ -5636,20 +6246,48 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B49" s="14" t="n"/>
-      <c r="C49" s="14" t="n"/>
-      <c r="D49" s="14" t="n"/>
-      <c r="E49" s="14" t="n"/>
-      <c r="F49" s="14" t="n"/>
-      <c r="G49" s="14" t="n"/>
-      <c r="H49" s="14" t="n"/>
-      <c r="I49" s="14" t="n"/>
-      <c r="J49" s="14" t="n"/>
-      <c r="K49" s="8" t="n"/>
-      <c r="L49" s="8" t="n"/>
-      <c r="M49" s="8" t="n"/>
-      <c r="N49" s="8" t="n"/>
-      <c r="O49" s="8" t="n"/>
+      <c r="B49" s="14" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="C49" s="14" t="n">
+        <v>0.5487</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>0.6148</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>0.6444</v>
+      </c>
+      <c r="G49" s="14" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="I49" s="14" t="n">
+        <v>0.5505</v>
+      </c>
+      <c r="J49" s="14" t="n">
+        <v>10.63372745215042</v>
+      </c>
+      <c r="K49" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="L49" s="15" t="n">
+        <v>51.146</v>
+      </c>
+      <c r="M49" s="15" t="n">
+        <v>40.16</v>
+      </c>
+      <c r="N49" s="15" t="n">
+        <v>16.29100166550789</v>
+      </c>
+      <c r="O49" s="15" t="n">
+        <v>35.14925041637697</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -6339,15 +6977,33 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="14" t="n"/>
-      <c r="I14" s="14" t="n"/>
-      <c r="J14" s="14" t="n"/>
+      <c r="B14" s="14" t="n">
+        <v>0.8612</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>0.8303</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>0.7098</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>0.6867</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>0.4369</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>9.759640166882043</v>
+      </c>
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
@@ -6409,15 +7065,33 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="14" t="n"/>
-      <c r="I16" s="14" t="n"/>
-      <c r="J16" s="14" t="n"/>
+      <c r="B16" s="14" t="n">
+        <v>0.8381999999999999</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>0.7978</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>0.6106</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>0.6433</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>0.6132</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>0.6028</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>13.39202503577152</v>
+      </c>
       <c r="K16" s="8" t="n"/>
       <c r="L16" s="8" t="n"/>
       <c r="M16" s="8" t="n"/>
@@ -6430,15 +7104,33 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-      <c r="H17" s="14" t="n"/>
-      <c r="I17" s="14" t="n"/>
-      <c r="J17" s="14" t="n"/>
+      <c r="B17" s="14" t="n">
+        <v>0.8578</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>0.8014</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>0.6593</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>0.6669</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>0.6444</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>0.6326000000000001</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>11.05066230567778</v>
+      </c>
       <c r="K17" s="8" t="n"/>
       <c r="L17" s="8" t="n"/>
       <c r="M17" s="8" t="n"/>
@@ -6870,15 +7562,33 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
+      <c r="B27" s="14" t="n">
+        <v>0.8749</v>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>0.7645</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>0.7364000000000001</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>0.8232</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>0.6109</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>0.7193000000000001</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>7.855145447281187</v>
+      </c>
       <c r="K27" s="7" t="n"/>
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
@@ -6891,20 +7601,38 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
-      <c r="G28" s="9" t="n"/>
-      <c r="H28" s="9" t="n"/>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="7" t="n"/>
-      <c r="L28" s="7" t="n"/>
-      <c r="M28" s="7" t="n"/>
-      <c r="N28" s="7" t="n"/>
-      <c r="O28" s="7" t="n"/>
+      <c r="B28" s="14" t="n">
+        <v>0.8749</v>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>0.7978</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>0.7665</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>0.7372</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>0.8245</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>0.6092</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>0.7214</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>7.898685692338934</v>
+      </c>
+      <c r="K28" s="8" t="n"/>
+      <c r="L28" s="8" t="n"/>
+      <c r="M28" s="8" t="n"/>
+      <c r="N28" s="8" t="n"/>
+      <c r="O28" s="8" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
@@ -6912,15 +7640,33 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
+      <c r="B29" s="14" t="n">
+        <v>0.8728</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>0.7978</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>0.7416</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>0.8047</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>0.5904</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>0.7096</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>8.675230072278056</v>
+      </c>
       <c r="K29" s="7" t="n"/>
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
@@ -6933,15 +7679,17 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="9" t="n"/>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="14" t="n">
+        <v>9.900163541911819</v>
+      </c>
       <c r="K30" s="7" t="n"/>
       <c r="L30" s="7" t="n"/>
       <c r="M30" s="7" t="n"/>
@@ -6954,15 +7702,17 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="9" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="14" t="n"/>
+      <c r="J31" s="14" t="n">
+        <v>12.77595844480453</v>
+      </c>
       <c r="K31" s="7" t="n"/>
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
@@ -8151,20 +8901,48 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="14" t="n"/>
-      <c r="I16" s="14" t="n"/>
-      <c r="J16" s="14" t="n"/>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="8" t="n"/>
-      <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n"/>
-      <c r="O16" s="8" t="n"/>
+      <c r="B16" s="14" t="n">
+        <v>0.8327</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>0.8339</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>0.6388</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>0.6748</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>0.5854</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>0.6158</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>12.14602633146553</v>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="L16" s="15" t="n">
+        <v>75.024</v>
+      </c>
+      <c r="M16" s="15" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="N16" s="15" t="n">
+        <v>71.83695628476083</v>
+      </c>
+      <c r="O16" s="15" t="n">
+        <v>68.73523907119021</v>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -8172,20 +8950,48 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-      <c r="H17" s="14" t="n"/>
-      <c r="I17" s="14" t="n"/>
-      <c r="J17" s="14" t="n"/>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="8" t="n"/>
-      <c r="M17" s="8" t="n"/>
-      <c r="N17" s="8" t="n"/>
-      <c r="O17" s="8" t="n"/>
+      <c r="B17" s="14" t="n">
+        <v>0.8529</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>0.8303</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>0.6742</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>0.6233</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>0.4044</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>10.9043515065757</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>76.44999999999999</v>
+      </c>
+      <c r="M17" s="15" t="n">
+        <v>47.59999999999999</v>
+      </c>
+      <c r="N17" s="15" t="n">
+        <v>75.36291116944828</v>
+      </c>
+      <c r="O17" s="15" t="n">
+        <v>70.22822779236206</v>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -8568,15 +9374,33 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="14" t="n"/>
-      <c r="E25" s="14" t="n"/>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="14" t="n"/>
-      <c r="H25" s="14" t="n"/>
-      <c r="I25" s="14" t="n"/>
-      <c r="J25" s="14" t="n"/>
+      <c r="B25" s="14" t="n">
+        <v>0.8431</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0.7401</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>0.6661</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>0.6938</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.7748</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0.5085</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>0.6592</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>11.50699608149418</v>
+      </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -8875,20 +9699,48 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="14" t="n"/>
-      <c r="E32" s="14" t="n"/>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="14" t="n"/>
-      <c r="H32" s="14" t="n"/>
-      <c r="I32" s="14" t="n"/>
-      <c r="J32" s="14" t="n"/>
-      <c r="K32" s="8" t="n"/>
-      <c r="L32" s="8" t="n"/>
-      <c r="M32" s="8" t="n"/>
-      <c r="N32" s="8" t="n"/>
-      <c r="O32" s="8" t="n"/>
+      <c r="B32" s="14" t="n">
+        <v>0.8651</v>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>0.8159</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>0.6273</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>0.6709000000000001</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="G32" s="14" t="n">
+        <v>0.4522</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="I32" s="14" t="n">
+        <v>0.6443</v>
+      </c>
+      <c r="J32" s="14" t="n">
+        <v>12.38364626456971</v>
+      </c>
+      <c r="K32" s="15" t="n">
+        <v>72</v>
+      </c>
+      <c r="L32" s="15" t="n">
+        <v>72.828</v>
+      </c>
+      <c r="M32" s="15" t="n">
+        <v>37.84</v>
+      </c>
+      <c r="N32" s="15" t="n">
+        <v>65.31095737068868</v>
+      </c>
+      <c r="O32" s="15" t="n">
+        <v>61.99473934267218</v>
+      </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
@@ -8896,20 +9748,48 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n"/>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="14" t="n"/>
-      <c r="E33" s="14" t="n"/>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="14" t="n"/>
-      <c r="H33" s="14" t="n"/>
-      <c r="I33" s="14" t="n"/>
-      <c r="J33" s="14" t="n"/>
-      <c r="K33" s="8" t="n"/>
-      <c r="L33" s="8" t="n"/>
-      <c r="M33" s="8" t="n"/>
-      <c r="N33" s="8" t="n"/>
-      <c r="O33" s="8" t="n"/>
+      <c r="B33" s="14" t="n">
+        <v>0.8633</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>0.6699000000000001</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>0.7032</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>0.7521</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>0.6717</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>10.85981490695986</v>
+      </c>
+      <c r="K33" s="15" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="L33" s="15" t="n">
+        <v>73.95200000000001</v>
+      </c>
+      <c r="M33" s="15" t="n">
+        <v>40.88</v>
+      </c>
+      <c r="N33" s="15" t="n">
+        <v>70.29902319559507</v>
+      </c>
+      <c r="O33" s="15" t="n">
+        <v>65.18275579889877</v>
+      </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
@@ -9106,20 +9986,48 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n"/>
-      <c r="C43" s="9" t="n"/>
-      <c r="D43" s="9" t="n"/>
-      <c r="E43" s="9" t="n"/>
-      <c r="F43" s="9" t="n"/>
-      <c r="G43" s="9" t="n"/>
-      <c r="H43" s="9" t="n"/>
-      <c r="I43" s="9" t="n"/>
-      <c r="J43" s="9" t="n"/>
-      <c r="K43" s="7" t="n"/>
-      <c r="L43" s="7" t="n"/>
-      <c r="M43" s="7" t="n"/>
-      <c r="N43" s="7" t="n"/>
-      <c r="O43" s="7" t="n"/>
+      <c r="B43" s="14" t="n">
+        <v>0.8046</v>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>0.6956</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>0.6709000000000001</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>0.7445000000000001</v>
+      </c>
+      <c r="G43" s="14" t="n">
+        <v>0.4488</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I43" s="14" t="n">
+        <v>0.6441</v>
+      </c>
+      <c r="J43" s="14" t="n">
+        <v>7.553345573106815</v>
+      </c>
+      <c r="K43" s="14" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="L43" s="14" t="n">
+        <v>56.742</v>
+      </c>
+      <c r="M43" s="14" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="N43" s="14" t="n">
+        <v>19.43151262672127</v>
+      </c>
+      <c r="O43" s="14" t="n">
+        <v>39.60837815668032</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -9127,20 +10035,48 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n"/>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="9" t="n"/>
-      <c r="E44" s="9" t="n"/>
-      <c r="F44" s="9" t="n"/>
-      <c r="G44" s="9" t="n"/>
-      <c r="H44" s="9" t="n"/>
-      <c r="I44" s="9" t="n"/>
-      <c r="J44" s="9" t="n"/>
-      <c r="K44" s="7" t="n"/>
-      <c r="L44" s="7" t="n"/>
-      <c r="M44" s="7" t="n"/>
-      <c r="N44" s="7" t="n"/>
-      <c r="O44" s="7" t="n"/>
+      <c r="B44" s="14" t="n">
+        <v>0.8064</v>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>0.6895</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>0.6929</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>0.6685</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>0.7374000000000001</v>
+      </c>
+      <c r="G44" s="14" t="n">
+        <v>0.4522</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="I44" s="14" t="n">
+        <v>0.6415999999999999</v>
+      </c>
+      <c r="J44" s="14" t="n">
+        <v>7.626390524815606</v>
+      </c>
+      <c r="K44" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="L44" s="14" t="n">
+        <v>56.34200000000001</v>
+      </c>
+      <c r="M44" s="14" t="n">
+        <v>45.72</v>
+      </c>
+      <c r="N44" s="14" t="n">
+        <v>19.2875362466497</v>
+      </c>
+      <c r="O44" s="14" t="n">
+        <v>39.33738406166243</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -9148,20 +10084,48 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B45" s="9" t="n"/>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="9" t="n"/>
-      <c r="F45" s="9" t="n"/>
-      <c r="G45" s="9" t="n"/>
-      <c r="H45" s="9" t="n"/>
-      <c r="I45" s="9" t="n"/>
-      <c r="J45" s="9" t="n"/>
-      <c r="K45" s="7" t="n"/>
-      <c r="L45" s="7" t="n"/>
-      <c r="M45" s="7" t="n"/>
-      <c r="N45" s="7" t="n"/>
-      <c r="O45" s="7" t="n"/>
+      <c r="B45" s="14" t="n">
+        <v>0.7942</v>
+      </c>
+      <c r="C45" s="14" t="n">
+        <v>0.5957</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>0.6748</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>0.7146</v>
+      </c>
+      <c r="G45" s="14" t="n">
+        <v>0.4275</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="I45" s="14" t="n">
+        <v>0.6185</v>
+      </c>
+      <c r="J45" s="14" t="n">
+        <v>8.158241708612751</v>
+      </c>
+      <c r="K45" s="14" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="L45" s="14" t="n">
+        <v>55.19799999999999</v>
+      </c>
+      <c r="M45" s="14" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="N45" s="14" t="n">
+        <v>18.34607017282345</v>
+      </c>
+      <c r="O45" s="14" t="n">
+        <v>38.06601754320586</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -9169,20 +10133,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B46" s="9" t="n"/>
-      <c r="C46" s="9" t="n"/>
-      <c r="D46" s="9" t="n"/>
-      <c r="E46" s="9" t="n"/>
-      <c r="F46" s="9" t="n"/>
-      <c r="G46" s="9" t="n"/>
-      <c r="H46" s="9" t="n"/>
-      <c r="I46" s="9" t="n"/>
-      <c r="J46" s="9" t="n"/>
-      <c r="K46" s="7" t="n"/>
-      <c r="L46" s="7" t="n"/>
-      <c r="M46" s="7" t="n"/>
-      <c r="N46" s="7" t="n"/>
-      <c r="O46" s="7" t="n"/>
+      <c r="B46" s="14" t="n">
+        <v>0.7618</v>
+      </c>
+      <c r="C46" s="14" t="n">
+        <v>0.6029</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>0.6869</v>
+      </c>
+      <c r="G46" s="14" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I46" s="14" t="n">
+        <v>0.5978</v>
+      </c>
+      <c r="J46" s="14" t="n">
+        <v>8.973015140158076</v>
+      </c>
+      <c r="K46" s="14" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="L46" s="14" t="n">
+        <v>53.08000000000001</v>
+      </c>
+      <c r="M46" s="14" t="n">
+        <v>40.84</v>
+      </c>
+      <c r="N46" s="14" t="n">
+        <v>16.93793903801071</v>
+      </c>
+      <c r="O46" s="14" t="n">
+        <v>36.16448475950268</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -9190,20 +10182,48 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B47" s="9" t="n"/>
-      <c r="C47" s="9" t="n"/>
-      <c r="D47" s="9" t="n"/>
-      <c r="E47" s="9" t="n"/>
-      <c r="F47" s="9" t="n"/>
-      <c r="G47" s="9" t="n"/>
-      <c r="H47" s="9" t="n"/>
-      <c r="I47" s="9" t="n"/>
-      <c r="J47" s="9" t="n"/>
-      <c r="K47" s="7" t="n"/>
-      <c r="L47" s="7" t="n"/>
-      <c r="M47" s="7" t="n"/>
-      <c r="N47" s="7" t="n"/>
-      <c r="O47" s="7" t="n"/>
+      <c r="B47" s="14" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="C47" s="14" t="n">
+        <v>0.5343</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>0.5923</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>0.6338</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>0.6145</v>
+      </c>
+      <c r="G47" s="14" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="I47" s="14" t="n">
+        <v>0.5452</v>
+      </c>
+      <c r="J47" s="14" t="n">
+        <v>11.02700328989043</v>
+      </c>
+      <c r="K47" s="14" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="L47" s="14" t="n">
+        <v>49.306</v>
+      </c>
+      <c r="M47" s="14" t="n">
+        <v>37.48</v>
+      </c>
+      <c r="N47" s="14" t="n">
+        <v>16.29738738148025</v>
+      </c>
+      <c r="O47" s="14" t="n">
+        <v>33.72084684537006</v>
+      </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
@@ -9211,20 +10231,48 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B48" s="14" t="n"/>
-      <c r="C48" s="14" t="n"/>
-      <c r="D48" s="14" t="n"/>
-      <c r="E48" s="14" t="n"/>
-      <c r="F48" s="14" t="n"/>
-      <c r="G48" s="14" t="n"/>
-      <c r="H48" s="14" t="n"/>
-      <c r="I48" s="14" t="n"/>
-      <c r="J48" s="14" t="n"/>
-      <c r="K48" s="8" t="n"/>
-      <c r="L48" s="8" t="n"/>
-      <c r="M48" s="8" t="n"/>
-      <c r="N48" s="8" t="n"/>
-      <c r="O48" s="8" t="n"/>
+      <c r="B48" s="14" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="C48" s="14" t="n">
+        <v>0.5812</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>0.5694</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>0.6235000000000001</v>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>0.6258</v>
+      </c>
+      <c r="G48" s="14" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="I48" s="14" t="n">
+        <v>0.5402</v>
+      </c>
+      <c r="J48" s="14" t="n">
+        <v>11.69882850383852</v>
+      </c>
+      <c r="K48" s="15" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="L48" s="15" t="n">
+        <v>49.37200000000001</v>
+      </c>
+      <c r="M48" s="15" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="N48" s="15" t="n">
+        <v>16.62112287729039</v>
+      </c>
+      <c r="O48" s="15" t="n">
+        <v>34.4232807193226</v>
+      </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
@@ -9232,20 +10280,48 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B49" s="14" t="n"/>
-      <c r="C49" s="14" t="n"/>
-      <c r="D49" s="14" t="n"/>
-      <c r="E49" s="14" t="n"/>
-      <c r="F49" s="14" t="n"/>
-      <c r="G49" s="14" t="n"/>
-      <c r="H49" s="14" t="n"/>
-      <c r="I49" s="14" t="n"/>
-      <c r="J49" s="14" t="n"/>
-      <c r="K49" s="8" t="n"/>
-      <c r="L49" s="8" t="n"/>
-      <c r="M49" s="8" t="n"/>
-      <c r="N49" s="8" t="n"/>
-      <c r="O49" s="8" t="n"/>
+      <c r="B49" s="14" t="n">
+        <v>0.6719000000000001</v>
+      </c>
+      <c r="C49" s="14" t="n">
+        <v>0.6354</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>0.6084000000000001</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>0.6393</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>0.6637</v>
+      </c>
+      <c r="G49" s="14" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="I49" s="14" t="n">
+        <v>0.5701000000000001</v>
+      </c>
+      <c r="J49" s="14" t="n">
+        <v>10.25288565207447</v>
+      </c>
+      <c r="K49" s="15" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="L49" s="15" t="n">
+        <v>51.95</v>
+      </c>
+      <c r="M49" s="15" t="n">
+        <v>40.76000000000001</v>
+      </c>
+      <c r="N49" s="15" t="n">
+        <v>16.86712578660085</v>
+      </c>
+      <c r="O49" s="15" t="n">
+        <v>35.76928144665021</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -10023,15 +11099,33 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="14" t="n"/>
-      <c r="I16" s="14" t="n"/>
-      <c r="J16" s="14" t="n"/>
+      <c r="B16" s="14" t="n">
+        <v>0.8483000000000001</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>0.8339</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>0.6375</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>0.6701</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>0.5939</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>0.6166</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>12.17765478688282</v>
+      </c>
       <c r="K16" s="8" t="n"/>
       <c r="L16" s="8" t="n"/>
       <c r="M16" s="8" t="n"/>
@@ -10484,15 +11578,33 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
+      <c r="B27" s="14" t="n">
+        <v>0.8749</v>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>0.7645</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>0.7364000000000001</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>0.8232</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>0.6109</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>0.7193000000000001</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>7.855145447281187</v>
+      </c>
       <c r="K27" s="7" t="n"/>
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
@@ -12002,15 +13114,33 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
+      <c r="B21" s="14" t="n">
+        <v>0.8749</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>0.7645</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>0.7364000000000001</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>0.8232</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>0.6109</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>0.7193000000000001</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>7.855145447281187</v>
+      </c>
       <c r="K21" s="7" t="n"/>
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
@@ -12023,15 +13153,17 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n">
+        <v>9.555099798748797</v>
+      </c>
       <c r="K22" s="7" t="n"/>
       <c r="L22" s="7" t="n"/>
       <c r="M22" s="7" t="n"/>
@@ -12044,15 +13176,17 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="14" t="n"/>
+      <c r="J23" s="14" t="n">
+        <v>27.57493867845532</v>
+      </c>
       <c r="K23" s="7" t="n"/>
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
@@ -12065,15 +13199,17 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="14" t="n">
+        <v>127.0739268153725</v>
+      </c>
       <c r="K24" s="7" t="n"/>
       <c r="L24" s="7" t="n"/>
       <c r="M24" s="7" t="n"/>
@@ -12086,15 +13222,17 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="14" t="n"/>
+      <c r="H25" s="14" t="n"/>
+      <c r="I25" s="14" t="n"/>
+      <c r="J25" s="14" t="n">
+        <v>1341.186220868133</v>
+      </c>
       <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
@@ -13786,20 +14924,48 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="7" t="n"/>
-      <c r="L33" s="7" t="n"/>
-      <c r="M33" s="7" t="n"/>
-      <c r="N33" s="7" t="n"/>
-      <c r="O33" s="7" t="n"/>
+      <c r="B33" s="14" t="n">
+        <v>0.8046</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>0.6956</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>0.6709000000000001</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>0.7445000000000001</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>0.4488</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>0.6441</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>7.553345573106815</v>
+      </c>
+      <c r="K33" s="14" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="L33" s="14" t="n">
+        <v>56.742</v>
+      </c>
+      <c r="M33" s="14" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="N33" s="14" t="n">
+        <v>19.43151262672127</v>
+      </c>
+      <c r="O33" s="14" t="n">
+        <v>39.60837815668032</v>
+      </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
@@ -13807,20 +14973,48 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n"/>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="9" t="n"/>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="9" t="n"/>
-      <c r="I34" s="9" t="n"/>
-      <c r="J34" s="9" t="n"/>
-      <c r="K34" s="7" t="n"/>
-      <c r="L34" s="7" t="n"/>
-      <c r="M34" s="7" t="n"/>
-      <c r="N34" s="7" t="n"/>
-      <c r="O34" s="7" t="n"/>
+      <c r="B34" s="14" t="n">
+        <v>0.7477</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>0.6715</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>0.6433</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>0.6688</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <v>0.6031</v>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>10.24640038545949</v>
+      </c>
+      <c r="K34" s="14" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="L34" s="14" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="M34" s="14" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="N34" s="14" t="n">
+        <v>17.19667459547421</v>
+      </c>
+      <c r="O34" s="14" t="n">
+        <v>33.28666864886856</v>
+      </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
@@ -13828,20 +15022,48 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="7" t="n"/>
-      <c r="L35" s="7" t="n"/>
-      <c r="M35" s="7" t="n"/>
-      <c r="N35" s="7" t="n"/>
-      <c r="O35" s="7" t="n"/>
+      <c r="B35" s="14" t="n">
+        <v>0.6229</v>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>0.5343</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>0.5288</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="G35" s="14" t="n">
+        <v>0.2491</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="I35" s="14" t="n">
+        <v>0.4233</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>51.21408891562781</v>
+      </c>
+      <c r="K35" s="14" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="L35" s="14" t="n">
+        <v>6.047999999999999</v>
+      </c>
+      <c r="M35" s="14" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N35" s="14" t="n">
+        <v>1.197022048871178</v>
+      </c>
+      <c r="O35" s="14" t="n">
+        <v>7.096255512217795</v>
+      </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
@@ -13849,20 +15071,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="9" t="n"/>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="7" t="n"/>
-      <c r="L36" s="7" t="n"/>
-      <c r="M36" s="7" t="n"/>
-      <c r="N36" s="7" t="n"/>
-      <c r="O36" s="7" t="n"/>
+      <c r="B36" s="14" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>0.5379</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>0.4909</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>0.2167</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="I36" s="14" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="J36" s="14" t="n">
+        <v>140.1137265288566</v>
+      </c>
+      <c r="K36" s="14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L36" s="14" t="n">
+        <v>4.172</v>
+      </c>
+      <c r="M36" s="14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N36" s="14" t="n">
+        <v>0.1007293313612485</v>
+      </c>
+      <c r="O36" s="14" t="n">
+        <v>1.618182332840312</v>
+      </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
@@ -13870,20 +15120,48 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="7" t="n"/>
-      <c r="L37" s="7" t="n"/>
-      <c r="M37" s="7" t="n"/>
-      <c r="N37" s="7" t="n"/>
-      <c r="O37" s="7" t="n"/>
+      <c r="B37" s="14" t="n">
+        <v>0.5927</v>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="G37" s="14" t="n">
+        <v>0.2483</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>1366.55907938144</v>
+      </c>
+      <c r="K37" s="14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="14" t="n">
+        <v>0.375</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -14926,15 +16204,33 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
+      <c r="B21" s="14" t="n">
+        <v>0.8749</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>0.7645</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>0.7364000000000001</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>0.8232</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>0.6109</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>0.7193000000000001</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>7.855145447281187</v>
+      </c>
       <c r="K21" s="7" t="n"/>
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
@@ -14947,15 +16243,33 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
+      <c r="B22" s="14" t="n">
+        <v>0.7963</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>0.6853</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>0.6022</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>0.7231</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>0.4659</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>11.54656722841926</v>
+      </c>
       <c r="K22" s="7" t="n"/>
       <c r="L22" s="7" t="n"/>
       <c r="M22" s="7" t="n"/>
@@ -14968,15 +16282,33 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
+      <c r="B23" s="14" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>0.4949</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>0.2363</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>43.99941870370173</v>
+      </c>
       <c r="K23" s="7" t="n"/>
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
@@ -14989,15 +16321,33 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
+      <c r="B24" s="14" t="n">
+        <v>0.5009</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>0.4693</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>0.5091</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>200.3270629362775</v>
+      </c>
       <c r="K24" s="7" t="n"/>
       <c r="L24" s="7" t="n"/>
       <c r="M24" s="7" t="n"/>
@@ -15010,15 +16360,33 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
+      <c r="B25" s="14" t="n">
+        <v>0.5318000000000001</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0.5379</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>0.2696</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>0.5083</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0.2457</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>1832.389631095462</v>
+      </c>
       <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
@@ -16710,20 +18078,48 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="7" t="n"/>
-      <c r="L33" s="7" t="n"/>
-      <c r="M33" s="7" t="n"/>
-      <c r="N33" s="7" t="n"/>
-      <c r="O33" s="7" t="n"/>
+      <c r="B33" s="14" t="n">
+        <v>0.8046</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>0.6956</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>0.6709000000000001</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>0.7445000000000001</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>0.4488</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>0.6441</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>7.553345573106815</v>
+      </c>
+      <c r="K33" s="14" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="L33" s="14" t="n">
+        <v>56.742</v>
+      </c>
+      <c r="M33" s="14" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="N33" s="14" t="n">
+        <v>19.43151262672127</v>
+      </c>
+      <c r="O33" s="14" t="n">
+        <v>39.60837815668032</v>
+      </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
@@ -16731,20 +18127,48 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n"/>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="9" t="n"/>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="9" t="n"/>
-      <c r="I34" s="9" t="n"/>
-      <c r="J34" s="9" t="n"/>
-      <c r="K34" s="7" t="n"/>
-      <c r="L34" s="7" t="n"/>
-      <c r="M34" s="7" t="n"/>
-      <c r="N34" s="7" t="n"/>
-      <c r="O34" s="7" t="n"/>
+      <c r="B34" s="14" t="n">
+        <v>0.7171</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>0.5957</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>0.5507</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>0.5809</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>0.6481</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <v>0.5449000000000001</v>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>11.64691105377318</v>
+      </c>
+      <c r="K34" s="14" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="L34" s="14" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="M34" s="14" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="N34" s="14" t="n">
+        <v>16.18413356780169</v>
+      </c>
+      <c r="O34" s="14" t="n">
+        <v>32.25603339195042</v>
+      </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
@@ -16752,20 +18176,48 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="7" t="n"/>
-      <c r="L35" s="7" t="n"/>
-      <c r="M35" s="7" t="n"/>
-      <c r="N35" s="7" t="n"/>
-      <c r="O35" s="7" t="n"/>
+      <c r="B35" s="14" t="n">
+        <v>0.6217</v>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>0.5199</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>0.5036</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>0.4457</v>
+      </c>
+      <c r="G35" s="14" t="n">
+        <v>0.2218</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="I35" s="14" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>48.84028555572556</v>
+      </c>
+      <c r="K35" s="14" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="L35" s="14" t="n">
+        <v>25.988</v>
+      </c>
+      <c r="M35" s="14" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="N35" s="14" t="n">
+        <v>6.58458122265691</v>
+      </c>
+      <c r="O35" s="14" t="n">
+        <v>15.76314530566423</v>
+      </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
@@ -16773,20 +18225,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="9" t="n"/>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="7" t="n"/>
-      <c r="L36" s="7" t="n"/>
-      <c r="M36" s="7" t="n"/>
-      <c r="N36" s="7" t="n"/>
-      <c r="O36" s="7" t="n"/>
+      <c r="B36" s="14" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>0.4765</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>0.4878</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>0.2082</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="I36" s="14" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="J36" s="14" t="n">
+        <v>159.76276438729</v>
+      </c>
+      <c r="K36" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L36" s="14" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="M36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="14" t="n">
+        <v>0.08925383791503035</v>
+      </c>
+      <c r="O36" s="14" t="n">
+        <v>0.1288134594787576</v>
+      </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
@@ -16794,20 +18274,48 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="7" t="n"/>
-      <c r="L37" s="7" t="n"/>
-      <c r="M37" s="7" t="n"/>
-      <c r="N37" s="7" t="n"/>
-      <c r="O37" s="7" t="n"/>
+      <c r="B37" s="14" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>0.5028</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="G37" s="14" t="n">
+        <v>0.2193</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>392.3331744336636</v>
+      </c>
+      <c r="K37" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L37" s="14" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="M37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="14" t="n">
+        <v>0.08850000000000001</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -17850,15 +19358,33 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
+      <c r="B21" s="14" t="n">
+        <v>0.8749</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>0.7645</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>0.7364000000000001</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>0.8232</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>0.6109</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>0.7193000000000001</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>7.855145447281187</v>
+      </c>
       <c r="K21" s="7" t="n"/>
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
@@ -17871,15 +19397,33 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
+      <c r="B22" s="14" t="n">
+        <v>0.7917</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>0.7184</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>0.5856</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>0.5778</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>11.80012242122977</v>
+      </c>
       <c r="K22" s="7" t="n"/>
       <c r="L22" s="7" t="n"/>
       <c r="M22" s="7" t="n"/>
@@ -17892,15 +19436,33 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
+      <c r="B23" s="14" t="n">
+        <v>0.4446</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>0.5415</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>0.2304</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>92.03002914120208</v>
+      </c>
       <c r="K23" s="7" t="n"/>
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
@@ -17913,15 +19475,33 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
+      <c r="B24" s="14" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>0.5199</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>0.4901</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0.2304</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>335.8451896265885</v>
+      </c>
       <c r="K24" s="7" t="n"/>
       <c r="L24" s="7" t="n"/>
       <c r="M24" s="7" t="n"/>
@@ -17934,15 +19514,33 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
+      <c r="B25" s="14" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0.5306999999999999</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>0.2606</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>0.4909</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0.2321</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>580.808780723072</v>
+      </c>
       <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
@@ -19634,20 +21232,48 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="7" t="n"/>
-      <c r="L33" s="7" t="n"/>
-      <c r="M33" s="7" t="n"/>
-      <c r="N33" s="7" t="n"/>
-      <c r="O33" s="7" t="n"/>
+      <c r="B33" s="14" t="n">
+        <v>0.8046</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>0.6956</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>0.6709000000000001</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>0.7445000000000001</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>0.4488</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>0.6441</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>7.553345573106815</v>
+      </c>
+      <c r="K33" s="14" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="L33" s="14" t="n">
+        <v>56.742</v>
+      </c>
+      <c r="M33" s="14" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="N33" s="14" t="n">
+        <v>19.43151262672127</v>
+      </c>
+      <c r="O33" s="14" t="n">
+        <v>39.60837815668032</v>
+      </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
@@ -19655,20 +21281,48 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n"/>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="9" t="n"/>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="9" t="n"/>
-      <c r="I34" s="9" t="n"/>
-      <c r="J34" s="9" t="n"/>
-      <c r="K34" s="7" t="n"/>
-      <c r="L34" s="7" t="n"/>
-      <c r="M34" s="7" t="n"/>
-      <c r="N34" s="7" t="n"/>
-      <c r="O34" s="7" t="n"/>
+      <c r="B34" s="14" t="n">
+        <v>0.6284</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>0.5415</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>0.5493</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>0.6094000000000001</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <v>0.5096000000000001</v>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>12.95238841106029</v>
+      </c>
+      <c r="K34" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="L34" s="14" t="n">
+        <v>42.82599999999999</v>
+      </c>
+      <c r="M34" s="14" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="N34" s="14" t="n">
+        <v>13.2148270090556</v>
+      </c>
+      <c r="O34" s="14" t="n">
+        <v>28.5602067522639</v>
+      </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
@@ -19676,20 +21330,48 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="7" t="n"/>
-      <c r="L35" s="7" t="n"/>
-      <c r="M35" s="7" t="n"/>
-      <c r="N35" s="7" t="n"/>
-      <c r="O35" s="7" t="n"/>
+      <c r="B35" s="14" t="n">
+        <v>0.6162</v>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>0.5523</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>0.5209</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>0.4369</v>
+      </c>
+      <c r="G35" s="14" t="n">
+        <v>0.2432</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="I35" s="14" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>37.57091783378142</v>
+      </c>
+      <c r="K35" s="14" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="L35" s="14" t="n">
+        <v>16.894</v>
+      </c>
+      <c r="M35" s="14" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="N35" s="14" t="n">
+        <v>4.511653758687381</v>
+      </c>
+      <c r="O35" s="14" t="n">
+        <v>11.04641343967184</v>
+      </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
@@ -19697,20 +21379,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="9" t="n"/>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="7" t="n"/>
-      <c r="L36" s="7" t="n"/>
-      <c r="M36" s="7" t="n"/>
-      <c r="N36" s="7" t="n"/>
-      <c r="O36" s="7" t="n"/>
+      <c r="B36" s="14" t="n">
+        <v>0.4761</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>0.5054</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>0.5043</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>0.2491</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="I36" s="14" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="J36" s="14" t="n">
+        <v>95.89522111222092</v>
+      </c>
+      <c r="K36" s="14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L36" s="14" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="M36" s="14" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N36" s="14" t="n">
+        <v>0.6724964756104043</v>
+      </c>
+      <c r="O36" s="14" t="n">
+        <v>3.098624118902601</v>
+      </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
@@ -19718,20 +21428,48 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="7" t="n"/>
-      <c r="L37" s="7" t="n"/>
-      <c r="M37" s="7" t="n"/>
-      <c r="N37" s="7" t="n"/>
-      <c r="O37" s="7" t="n"/>
+      <c r="B37" s="14" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>0.5054</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>0.4886</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="G37" s="14" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>1129.345501091109</v>
+      </c>
+      <c r="K37" s="14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="14" t="n">
+        <v>0.6</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -20774,15 +22512,33 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
+      <c r="B21" s="14" t="n">
+        <v>0.8749</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>0.7645</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>0.7364000000000001</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>0.8232</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>0.6109</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>0.7193000000000001</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>7.855145447281187</v>
+      </c>
       <c r="K21" s="7" t="n"/>
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
@@ -20795,15 +22551,33 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
+      <c r="B22" s="14" t="n">
+        <v>0.6651</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>0.5379</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>0.6246</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>0.5699</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>0.6978</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>0.5558999999999999</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>12.40953345103332</v>
+      </c>
       <c r="K22" s="7" t="n"/>
       <c r="L22" s="7" t="n"/>
       <c r="M22" s="7" t="n"/>
@@ -20816,15 +22590,33 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
+      <c r="B23" s="14" t="n">
+        <v>0.4722</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>0.5306999999999999</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>0.5178</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>0.4529</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>136.8542127445664</v>
+      </c>
       <c r="K23" s="7" t="n"/>
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
@@ -20837,15 +22629,33 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
+      <c r="B24" s="14" t="n">
+        <v>0.4272</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>0.5122</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0.2389</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>30841.93069804118</v>
+      </c>
       <c r="K24" s="7" t="n"/>
       <c r="L24" s="7" t="n"/>
       <c r="M24" s="7" t="n"/>
@@ -20858,15 +22668,33 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
+      <c r="B25" s="14" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0.4874</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>0.5036</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.2513</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>400402.0716036924</v>
+      </c>
       <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
@@ -21849,20 +23677,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="14" t="n"/>
-      <c r="I14" s="14" t="n"/>
-      <c r="J14" s="14" t="n"/>
-      <c r="K14" s="8" t="n"/>
-      <c r="L14" s="8" t="n"/>
-      <c r="M14" s="8" t="n"/>
-      <c r="N14" s="8" t="n"/>
-      <c r="O14" s="8" t="n"/>
+      <c r="B14" s="14" t="n">
+        <v>0.8596</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>0.7978</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>0.6734</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>0.6471</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>9.873320773484789</v>
+      </c>
+      <c r="K14" s="15" t="n">
+        <v>84</v>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>81.876</v>
+      </c>
+      <c r="M14" s="15" t="n">
+        <v>79.47999999999999</v>
+      </c>
+      <c r="N14" s="15" t="n">
+        <v>77.58387847643465</v>
+      </c>
+      <c r="O14" s="15" t="n">
+        <v>80.73496961910865</v>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
@@ -21919,20 +23775,48 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="14" t="n"/>
-      <c r="I16" s="14" t="n"/>
-      <c r="J16" s="14" t="n"/>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="8" t="n"/>
-      <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n"/>
-      <c r="O16" s="8" t="n"/>
+      <c r="B16" s="14" t="n">
+        <v>0.7862</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>0.7942</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>0.5835</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>0.6235000000000001</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>0.5792</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>21.05779759200868</v>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="L16" s="15" t="n">
+        <v>79.47200000000001</v>
+      </c>
+      <c r="M16" s="15" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="N16" s="15" t="n">
+        <v>71.59585454471909</v>
+      </c>
+      <c r="O16" s="15" t="n">
+        <v>72.28696363617978</v>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -21940,20 +23824,48 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-      <c r="H17" s="14" t="n"/>
-      <c r="I17" s="14" t="n"/>
-      <c r="J17" s="14" t="n"/>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="8" t="n"/>
-      <c r="M17" s="8" t="n"/>
-      <c r="N17" s="8" t="n"/>
-      <c r="O17" s="8" t="n"/>
+      <c r="B17" s="14" t="n">
+        <v>0.8324</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>0.7978</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>0.6491</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>0.6567</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>0.6149</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>12.02148013479941</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>79.71799999999999</v>
+      </c>
+      <c r="M17" s="15" t="n">
+        <v>66.03999999999999</v>
+      </c>
+      <c r="N17" s="15" t="n">
+        <v>75.768596181484</v>
+      </c>
+      <c r="O17" s="15" t="n">
+        <v>76.106649045371</v>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -22336,15 +24248,33 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="14" t="n"/>
-      <c r="E25" s="14" t="n"/>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="14" t="n"/>
-      <c r="H25" s="14" t="n"/>
-      <c r="I25" s="14" t="n"/>
-      <c r="J25" s="14" t="n"/>
+      <c r="B25" s="14" t="n">
+        <v>0.8495</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>0.6173999999999999</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>0.6567</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.7609</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0.4846</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>0.6384</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>12.51776028562483</v>
+      </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -22643,20 +24573,48 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="14" t="n"/>
-      <c r="E32" s="14" t="n"/>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="14" t="n"/>
-      <c r="H32" s="14" t="n"/>
-      <c r="I32" s="14" t="n"/>
-      <c r="J32" s="14" t="n"/>
-      <c r="K32" s="8" t="n"/>
-      <c r="L32" s="8" t="n"/>
-      <c r="M32" s="8" t="n"/>
-      <c r="N32" s="8" t="n"/>
-      <c r="O32" s="8" t="n"/>
+      <c r="B32" s="14" t="n">
+        <v>0.8327</v>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>0.7292</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>0.5642</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>0.6488</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>0.6957</v>
+      </c>
+      <c r="G32" s="14" t="n">
+        <v>0.4172</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I32" s="14" t="n">
+        <v>0.6054</v>
+      </c>
+      <c r="J32" s="14" t="n">
+        <v>15.27786282680619</v>
+      </c>
+      <c r="K32" s="15" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="L32" s="15" t="n">
+        <v>72.23399999999999</v>
+      </c>
+      <c r="M32" s="15" t="n">
+        <v>51.23999999999999</v>
+      </c>
+      <c r="N32" s="15" t="n">
+        <v>63.89282723555279</v>
+      </c>
+      <c r="O32" s="15" t="n">
+        <v>64.96670680888819</v>
+      </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
@@ -22664,20 +24622,48 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n"/>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="14" t="n"/>
-      <c r="E33" s="14" t="n"/>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="14" t="n"/>
-      <c r="H33" s="14" t="n"/>
-      <c r="I33" s="14" t="n"/>
-      <c r="J33" s="14" t="n"/>
-      <c r="K33" s="8" t="n"/>
-      <c r="L33" s="8" t="n"/>
-      <c r="M33" s="8" t="n"/>
-      <c r="N33" s="8" t="n"/>
-      <c r="O33" s="8" t="n"/>
+      <c r="B33" s="14" t="n">
+        <v>0.8526</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>0.7622</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>11.53374444649607</v>
+      </c>
+      <c r="K33" s="15" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="L33" s="15" t="n">
+        <v>74.896</v>
+      </c>
+      <c r="M33" s="15" t="n">
+        <v>55.48</v>
+      </c>
+      <c r="N33" s="15" t="n">
+        <v>71.39572640007866</v>
+      </c>
+      <c r="O33" s="15" t="n">
+        <v>69.89293160001966</v>
+      </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
@@ -22874,20 +24860,48 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n"/>
-      <c r="C43" s="9" t="n"/>
-      <c r="D43" s="9" t="n"/>
-      <c r="E43" s="9" t="n"/>
-      <c r="F43" s="9" t="n"/>
-      <c r="G43" s="9" t="n"/>
-      <c r="H43" s="9" t="n"/>
-      <c r="I43" s="9" t="n"/>
-      <c r="J43" s="9" t="n"/>
-      <c r="K43" s="7" t="n"/>
-      <c r="L43" s="7" t="n"/>
-      <c r="M43" s="7" t="n"/>
-      <c r="N43" s="7" t="n"/>
-      <c r="O43" s="7" t="n"/>
+      <c r="B43" s="14" t="n">
+        <v>0.8046</v>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>0.6956</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>0.6709000000000001</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>0.7445000000000001</v>
+      </c>
+      <c r="G43" s="14" t="n">
+        <v>0.4488</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I43" s="14" t="n">
+        <v>0.6441</v>
+      </c>
+      <c r="J43" s="14" t="n">
+        <v>7.553345573106815</v>
+      </c>
+      <c r="K43" s="14" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="L43" s="14" t="n">
+        <v>56.742</v>
+      </c>
+      <c r="M43" s="14" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="N43" s="14" t="n">
+        <v>19.43151262672127</v>
+      </c>
+      <c r="O43" s="14" t="n">
+        <v>39.60837815668032</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -22895,20 +24909,48 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n"/>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="9" t="n"/>
-      <c r="E44" s="9" t="n"/>
-      <c r="F44" s="9" t="n"/>
-      <c r="G44" s="9" t="n"/>
-      <c r="H44" s="9" t="n"/>
-      <c r="I44" s="9" t="n"/>
-      <c r="J44" s="9" t="n"/>
-      <c r="K44" s="7" t="n"/>
-      <c r="L44" s="7" t="n"/>
-      <c r="M44" s="7" t="n"/>
-      <c r="N44" s="7" t="n"/>
-      <c r="O44" s="7" t="n"/>
+      <c r="B44" s="14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>0.6787</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>0.6932</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>0.6669</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>0.7433</v>
+      </c>
+      <c r="G44" s="14" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I44" s="14" t="n">
+        <v>0.6381</v>
+      </c>
+      <c r="J44" s="14" t="n">
+        <v>7.650454188396908</v>
+      </c>
+      <c r="K44" s="14" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="L44" s="14" t="n">
+        <v>56.49200000000001</v>
+      </c>
+      <c r="M44" s="14" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="N44" s="14" t="n">
+        <v>19.56339931214147</v>
+      </c>
+      <c r="O44" s="14" t="n">
+        <v>39.33884982803537</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -22916,20 +24958,48 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B45" s="9" t="n"/>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="9" t="n"/>
-      <c r="F45" s="9" t="n"/>
-      <c r="G45" s="9" t="n"/>
-      <c r="H45" s="9" t="n"/>
-      <c r="I45" s="9" t="n"/>
-      <c r="J45" s="9" t="n"/>
-      <c r="K45" s="7" t="n"/>
-      <c r="L45" s="7" t="n"/>
-      <c r="M45" s="7" t="n"/>
-      <c r="N45" s="7" t="n"/>
-      <c r="O45" s="7" t="n"/>
+      <c r="B45" s="14" t="n">
+        <v>0.7746</v>
+      </c>
+      <c r="C45" s="14" t="n">
+        <v>0.5596</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>0.6742</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G45" s="14" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="I45" s="14" t="n">
+        <v>0.6041</v>
+      </c>
+      <c r="J45" s="14" t="n">
+        <v>8.599938170982416</v>
+      </c>
+      <c r="K45" s="14" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="L45" s="14" t="n">
+        <v>54.932</v>
+      </c>
+      <c r="M45" s="14" t="n">
+        <v>43.28</v>
+      </c>
+      <c r="N45" s="14" t="n">
+        <v>16.89055453685208</v>
+      </c>
+      <c r="O45" s="14" t="n">
+        <v>37.40063863421302</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -22937,20 +25007,48 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B46" s="9" t="n"/>
-      <c r="C46" s="9" t="n"/>
-      <c r="D46" s="9" t="n"/>
-      <c r="E46" s="9" t="n"/>
-      <c r="F46" s="9" t="n"/>
-      <c r="G46" s="9" t="n"/>
-      <c r="H46" s="9" t="n"/>
-      <c r="I46" s="9" t="n"/>
-      <c r="J46" s="9" t="n"/>
-      <c r="K46" s="7" t="n"/>
-      <c r="L46" s="7" t="n"/>
-      <c r="M46" s="7" t="n"/>
-      <c r="N46" s="7" t="n"/>
-      <c r="O46" s="7" t="n"/>
+      <c r="B46" s="14" t="n">
+        <v>0.6942</v>
+      </c>
+      <c r="C46" s="14" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>0.6269</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>0.6227</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>0.6675</v>
+      </c>
+      <c r="G46" s="14" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I46" s="14" t="n">
+        <v>0.5614</v>
+      </c>
+      <c r="J46" s="14" t="n">
+        <v>10.70749056472706</v>
+      </c>
+      <c r="K46" s="14" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="L46" s="14" t="n">
+        <v>48.80399999999999</v>
+      </c>
+      <c r="M46" s="14" t="n">
+        <v>38.56</v>
+      </c>
+      <c r="N46" s="14" t="n">
+        <v>13.95800961470329</v>
+      </c>
+      <c r="O46" s="14" t="n">
+        <v>33.68050240367582</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -22958,20 +25056,48 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B47" s="9" t="n"/>
-      <c r="C47" s="9" t="n"/>
-      <c r="D47" s="9" t="n"/>
-      <c r="E47" s="9" t="n"/>
-      <c r="F47" s="9" t="n"/>
-      <c r="G47" s="9" t="n"/>
-      <c r="H47" s="9" t="n"/>
-      <c r="I47" s="9" t="n"/>
-      <c r="J47" s="9" t="n"/>
-      <c r="K47" s="7" t="n"/>
-      <c r="L47" s="7" t="n"/>
-      <c r="M47" s="7" t="n"/>
-      <c r="N47" s="7" t="n"/>
-      <c r="O47" s="7" t="n"/>
+      <c r="B47" s="14" t="n">
+        <v>0.6254</v>
+      </c>
+      <c r="C47" s="14" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>0.4746</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>0.5800999999999999</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>0.5265</v>
+      </c>
+      <c r="G47" s="14" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I47" s="14" t="n">
+        <v>0.4784</v>
+      </c>
+      <c r="J47" s="14" t="n">
+        <v>23.40360062650884</v>
+      </c>
+      <c r="K47" s="14" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="L47" s="14" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="M47" s="14" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="N47" s="14" t="n">
+        <v>5.894197068895016</v>
+      </c>
+      <c r="O47" s="14" t="n">
+        <v>15.59354926722376</v>
+      </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
@@ -22979,20 +25105,48 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B48" s="14" t="n"/>
-      <c r="C48" s="14" t="n"/>
-      <c r="D48" s="14" t="n"/>
-      <c r="E48" s="14" t="n"/>
-      <c r="F48" s="14" t="n"/>
-      <c r="G48" s="14" t="n"/>
-      <c r="H48" s="14" t="n"/>
-      <c r="I48" s="14" t="n"/>
-      <c r="J48" s="14" t="n"/>
-      <c r="K48" s="8" t="n"/>
-      <c r="L48" s="8" t="n"/>
-      <c r="M48" s="8" t="n"/>
-      <c r="N48" s="8" t="n"/>
-      <c r="O48" s="8" t="n"/>
+      <c r="B48" s="14" t="n">
+        <v>0.6232</v>
+      </c>
+      <c r="C48" s="14" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>0.4731</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>0.5328000000000001</v>
+      </c>
+      <c r="G48" s="14" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I48" s="14" t="n">
+        <v>0.4786</v>
+      </c>
+      <c r="J48" s="14" t="n">
+        <v>26.50571853167642</v>
+      </c>
+      <c r="K48" s="15" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="L48" s="15" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="M48" s="15" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="N48" s="15" t="n">
+        <v>9.181130788654585</v>
+      </c>
+      <c r="O48" s="15" t="n">
+        <v>21.51778269716365</v>
+      </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
@@ -23000,20 +25154,48 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B49" s="14" t="n"/>
-      <c r="C49" s="14" t="n"/>
-      <c r="D49" s="14" t="n"/>
-      <c r="E49" s="14" t="n"/>
-      <c r="F49" s="14" t="n"/>
-      <c r="G49" s="14" t="n"/>
-      <c r="H49" s="14" t="n"/>
-      <c r="I49" s="14" t="n"/>
-      <c r="J49" s="14" t="n"/>
-      <c r="K49" s="8" t="n"/>
-      <c r="L49" s="8" t="n"/>
-      <c r="M49" s="8" t="n"/>
-      <c r="N49" s="8" t="n"/>
-      <c r="O49" s="8" t="n"/>
+      <c r="B49" s="14" t="n">
+        <v>0.6453</v>
+      </c>
+      <c r="C49" s="14" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>0.5616</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>0.6046</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>0.6309</v>
+      </c>
+      <c r="G49" s="14" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="I49" s="14" t="n">
+        <v>0.5259</v>
+      </c>
+      <c r="J49" s="14" t="n">
+        <v>14.84132782977127</v>
+      </c>
+      <c r="K49" s="15" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="L49" s="15" t="n">
+        <v>43.88399999999999</v>
+      </c>
+      <c r="M49" s="15" t="n">
+        <v>33.64</v>
+      </c>
+      <c r="N49" s="15" t="n">
+        <v>12.98345199764336</v>
+      </c>
+      <c r="O49" s="15" t="n">
+        <v>30.65186299941084</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/剪枝结果-飞书.xlsx
+++ b/剪枝结果-飞书.xlsx
@@ -2774,19 +2774,19 @@
         <v>8.51760434113363</v>
       </c>
       <c r="K11" s="14" t="n">
-        <v>87.8</v>
+        <v>85.3</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>84.51799999999999</v>
+        <v>84.44200000000001</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>85.64</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>79.79091072052694</v>
+        <v>81.56239526741471</v>
       </c>
       <c r="O11" s="14" t="n">
-        <v>84.43722768013173</v>
+        <v>84.24609881685367</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -2920,9 +2920,15 @@
       <c r="J14" s="14" t="n">
         <v>9.857977828286456</v>
       </c>
-      <c r="K14" s="8" t="n"/>
-      <c r="L14" s="8" t="n"/>
-      <c r="M14" s="8" t="n"/>
+      <c r="K14" s="15" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>81.70999999999999</v>
+      </c>
+      <c r="M14" s="15" t="n">
+        <v>79.08</v>
+      </c>
       <c r="N14" s="8" t="n"/>
       <c r="O14" s="8" t="n"/>
     </row>
@@ -3008,9 +3014,15 @@
       <c r="J16" s="14" t="n">
         <v>21.4543478127974</v>
       </c>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="8" t="n"/>
-      <c r="M16" s="8" t="n"/>
+      <c r="K16" s="15" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="L16" s="15" t="n">
+        <v>79.348</v>
+      </c>
+      <c r="M16" s="15" t="n">
+        <v>56.96</v>
+      </c>
       <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n"/>
     </row>
@@ -3047,9 +3059,15 @@
       <c r="J17" s="14" t="n">
         <v>11.94241601793689</v>
       </c>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="8" t="n"/>
-      <c r="M17" s="8" t="n"/>
+      <c r="K17" s="15" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>79.444</v>
+      </c>
+      <c r="M17" s="15" t="n">
+        <v>64.28</v>
+      </c>
       <c r="N17" s="8" t="n"/>
       <c r="O17" s="8" t="n"/>
     </row>
@@ -6858,19 +6876,19 @@
         <v>8.51760434113363</v>
       </c>
       <c r="K11" s="14" t="n">
-        <v>87.8</v>
+        <v>85.3</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>84.51799999999999</v>
+        <v>84.44200000000001</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>85.64</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>79.79091072052694</v>
+        <v>81.56239526741471</v>
       </c>
       <c r="O11" s="14" t="n">
-        <v>84.43722768013173</v>
+        <v>84.24609881685367</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
@@ -7004,8 +7022,12 @@
       <c r="J14" s="14" t="n">
         <v>9.759640166882043</v>
       </c>
-      <c r="K14" s="8" t="n"/>
-      <c r="L14" s="8" t="n"/>
+      <c r="K14" s="15" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>79.102</v>
+      </c>
       <c r="M14" s="8" t="n"/>
       <c r="N14" s="8" t="n"/>
       <c r="O14" s="8" t="n"/>
@@ -7092,9 +7114,15 @@
       <c r="J16" s="14" t="n">
         <v>13.39202503577152</v>
       </c>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="8" t="n"/>
-      <c r="M16" s="8" t="n"/>
+      <c r="K16" s="15" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="L16" s="15" t="n">
+        <v>77.804</v>
+      </c>
+      <c r="M16" s="15" t="n">
+        <v>48.6</v>
+      </c>
       <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n"/>
     </row>
@@ -7131,9 +7159,15 @@
       <c r="J17" s="14" t="n">
         <v>11.05066230567778</v>
       </c>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="8" t="n"/>
-      <c r="M17" s="8" t="n"/>
+      <c r="K17" s="15" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>76.964</v>
+      </c>
+      <c r="M17" s="15" t="n">
+        <v>45.12</v>
+      </c>
       <c r="N17" s="8" t="n"/>
       <c r="O17" s="8" t="n"/>
     </row>
@@ -10892,19 +10926,19 @@
         <v>8.51760434113363</v>
       </c>
       <c r="K11" s="14" t="n">
-        <v>87.8</v>
+        <v>85.3</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>84.51799999999999</v>
+        <v>84.44200000000001</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>85.64</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>79.79091072052694</v>
+        <v>81.56239526741471</v>
       </c>
       <c r="O11" s="14" t="n">
-        <v>84.43722768013173</v>
+        <v>84.24609881685367</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -11038,7 +11072,9 @@
       <c r="J14" s="14" t="n">
         <v>9.793435793805299</v>
       </c>
-      <c r="K14" s="8" t="n"/>
+      <c r="K14" s="15" t="n">
+        <v>84.2</v>
+      </c>
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
       <c r="N14" s="8" t="n"/>
@@ -12560,19 +12596,19 @@
         <v>8.51760434113363</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>87.8</v>
+        <v>85.3</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>84.51799999999999</v>
+        <v>84.44200000000001</v>
       </c>
       <c r="M9" s="14" t="n">
-        <v>85.64</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>79.79091072052694</v>
+        <v>81.56239526741471</v>
       </c>
       <c r="O9" s="14" t="n">
-        <v>84.43722768013173</v>
+        <v>84.24609881685367</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -15650,19 +15686,19 @@
         <v>8.51760434113363</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>87.8</v>
+        <v>85.3</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>84.51799999999999</v>
+        <v>84.44200000000001</v>
       </c>
       <c r="M9" s="14" t="n">
-        <v>85.64</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>79.79091072052694</v>
+        <v>81.56239526741471</v>
       </c>
       <c r="O9" s="14" t="n">
-        <v>84.43722768013173</v>
+        <v>84.24609881685367</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -18804,19 +18840,19 @@
         <v>8.51760434113363</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>87.8</v>
+        <v>85.3</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>84.51799999999999</v>
+        <v>84.44200000000001</v>
       </c>
       <c r="M9" s="14" t="n">
-        <v>85.64</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>79.79091072052694</v>
+        <v>81.56239526741471</v>
       </c>
       <c r="O9" s="14" t="n">
-        <v>84.43722768013173</v>
+        <v>84.24609881685367</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -21958,19 +21994,19 @@
         <v>8.51760434113363</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>87.8</v>
+        <v>85.3</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>84.51799999999999</v>
+        <v>84.44200000000001</v>
       </c>
       <c r="M9" s="14" t="n">
-        <v>85.64</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>79.79091072052694</v>
+        <v>81.56239526741471</v>
       </c>
       <c r="O9" s="14" t="n">
-        <v>84.43722768013173</v>
+        <v>84.24609881685367</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/剪枝结果-飞书.xlsx
+++ b/剪枝结果-飞书.xlsx
@@ -7028,7 +7028,9 @@
       <c r="L14" s="15" t="n">
         <v>79.102</v>
       </c>
-      <c r="M14" s="8" t="n"/>
+      <c r="M14" s="15" t="n">
+        <v>66.12</v>
+      </c>
       <c r="N14" s="8" t="n"/>
       <c r="O14" s="8" t="n"/>
     </row>

--- a/剪枝结果-飞书.xlsx
+++ b/剪枝结果-飞书.xlsx
@@ -11077,7 +11077,9 @@
       <c r="K14" s="15" t="n">
         <v>84.2</v>
       </c>
-      <c r="L14" s="8" t="n"/>
+      <c r="L14" s="15" t="n">
+        <v>80.404</v>
+      </c>
       <c r="M14" s="8" t="n"/>
       <c r="N14" s="8" t="n"/>
       <c r="O14" s="8" t="n"/>

--- a/剪枝结果-飞书.xlsx
+++ b/剪枝结果-飞书.xlsx
@@ -2643,15 +2643,33 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="14" t="n"/>
-      <c r="J8" s="14" t="n"/>
+      <c r="B8" s="14" t="n">
+        <v>0.8381999999999999</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0.8087</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>0.6251</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0.6526999999999999</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>0.6965</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0.4369</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>0.6369</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>14.98162884162644</v>
+      </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2684,15 +2702,33 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
-      <c r="J9" s="14" t="n"/>
+      <c r="B9" s="14" t="n">
+        <v>0.8517</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>0.7762</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>0.6879</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0.6827</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0.7546</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>0.4838</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0.6656</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>10.17508977614515</v>
+      </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2929,8 +2965,12 @@
       <c r="M14" s="15" t="n">
         <v>79.08</v>
       </c>
-      <c r="N14" s="8" t="n"/>
-      <c r="O14" s="8" t="n"/>
+      <c r="N14" s="15" t="n">
+        <v>77.68287677743521</v>
+      </c>
+      <c r="O14" s="15" t="n">
+        <v>80.81821919435879</v>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
@@ -3023,8 +3063,12 @@
       <c r="M16" s="15" t="n">
         <v>56.96</v>
       </c>
-      <c r="N16" s="8" t="n"/>
-      <c r="O16" s="8" t="n"/>
+      <c r="N16" s="15" t="n">
+        <v>71.32275884415212</v>
+      </c>
+      <c r="O16" s="15" t="n">
+        <v>71.93268971103802</v>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -3068,8 +3112,12 @@
       <c r="M17" s="15" t="n">
         <v>64.28</v>
       </c>
-      <c r="N17" s="8" t="n"/>
-      <c r="O17" s="8" t="n"/>
+      <c r="N17" s="15" t="n">
+        <v>76.07087491557432</v>
+      </c>
+      <c r="O17" s="15" t="n">
+        <v>75.57371872889358</v>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -3393,15 +3441,33 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="14" t="n"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="14" t="n"/>
-      <c r="H24" s="14" t="n"/>
-      <c r="I24" s="14" t="n"/>
-      <c r="J24" s="14" t="n"/>
+      <c r="B24" s="14" t="n">
+        <v>0.8217</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>0.6029</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>0.5586</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>0.6306</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>0.6961000000000001</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0.4181</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>0.5809</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>15.40946848894207</v>
+      </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -3434,15 +3500,33 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="14" t="n"/>
-      <c r="E25" s="14" t="n"/>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="14" t="n"/>
-      <c r="H25" s="14" t="n"/>
-      <c r="I25" s="14" t="n"/>
-      <c r="J25" s="14" t="n"/>
+      <c r="B25" s="14" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0.7256</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>0.6191</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>0.6606</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.7609</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0.4812</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>0.6382</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>12.49607959892532</v>
+      </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -3523,11 +3607,21 @@
       <c r="J27" s="14" t="n">
         <v>7.855145447281187</v>
       </c>
-      <c r="K27" s="7" t="n"/>
-      <c r="L27" s="7" t="n"/>
-      <c r="M27" s="7" t="n"/>
-      <c r="N27" s="7" t="n"/>
-      <c r="O27" s="7" t="n"/>
+      <c r="K27" s="14" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="L27" s="14" t="n">
+        <v>82.968</v>
+      </c>
+      <c r="M27" s="14" t="n">
+        <v>83.36</v>
+      </c>
+      <c r="N27" s="14" t="n">
+        <v>83.11612778481857</v>
+      </c>
+      <c r="O27" s="14" t="n">
+        <v>84.03603194620464</v>
+      </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
@@ -6745,15 +6839,33 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="14" t="n"/>
-      <c r="J8" s="14" t="n"/>
+      <c r="B8" s="14" t="n">
+        <v>0.8547</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>0.6685</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0.6796</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>0.7066</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0.4497</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>0.6535</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>11.0829279186429</v>
+      </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6786,15 +6898,33 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
-      <c r="J9" s="14" t="n"/>
+      <c r="B9" s="14" t="n">
+        <v>0.8522999999999999</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>0.8014</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>0.7105</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0.6796</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0.7534</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>0.5077</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0.6778</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>9.589240670634753</v>
+      </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -7031,8 +7161,12 @@
       <c r="M14" s="15" t="n">
         <v>66.12</v>
       </c>
-      <c r="N14" s="8" t="n"/>
-      <c r="O14" s="8" t="n"/>
+      <c r="N14" s="15" t="n">
+        <v>75.76339063864515</v>
+      </c>
+      <c r="O14" s="15" t="n">
+        <v>76.27134765966129</v>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
@@ -7125,8 +7259,12 @@
       <c r="M16" s="15" t="n">
         <v>48.6</v>
       </c>
-      <c r="N16" s="8" t="n"/>
-      <c r="O16" s="8" t="n"/>
+      <c r="N16" s="15" t="n">
+        <v>70.94698961418374</v>
+      </c>
+      <c r="O16" s="15" t="n">
+        <v>69.11274740354594</v>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -7170,8 +7308,12 @@
       <c r="M17" s="15" t="n">
         <v>45.12</v>
       </c>
-      <c r="N17" s="8" t="n"/>
-      <c r="O17" s="8" t="n"/>
+      <c r="N17" s="15" t="n">
+        <v>74.18798261259997</v>
+      </c>
+      <c r="O17" s="15" t="n">
+        <v>69.34299565314998</v>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -7495,15 +7637,33 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="14" t="n"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="14" t="n"/>
-      <c r="H24" s="14" t="n"/>
-      <c r="I24" s="14" t="n"/>
-      <c r="J24" s="14" t="n"/>
+      <c r="B24" s="14" t="n">
+        <v>0.8012</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>0.6462</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>0.6036</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>0.6551</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>0.7113</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>13.86627246312579</v>
+      </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -7536,15 +7696,33 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="14" t="n"/>
-      <c r="E25" s="14" t="n"/>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="14" t="n"/>
-      <c r="H25" s="14" t="n"/>
-      <c r="I25" s="14" t="n"/>
-      <c r="J25" s="14" t="n"/>
+      <c r="B25" s="14" t="n">
+        <v>0.8453000000000001</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0.6715</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>0.6445</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>0.6803</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.7521</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0.4974</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>0.6393</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>12.06350600064571</v>
+      </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -7625,11 +7803,21 @@
       <c r="J27" s="14" t="n">
         <v>7.855145447281187</v>
       </c>
-      <c r="K27" s="7" t="n"/>
-      <c r="L27" s="7" t="n"/>
-      <c r="M27" s="7" t="n"/>
-      <c r="N27" s="7" t="n"/>
-      <c r="O27" s="7" t="n"/>
+      <c r="K27" s="14" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="L27" s="14" t="n">
+        <v>82.968</v>
+      </c>
+      <c r="M27" s="14" t="n">
+        <v>83.36</v>
+      </c>
+      <c r="N27" s="14" t="n">
+        <v>83.11612778481857</v>
+      </c>
+      <c r="O27" s="14" t="n">
+        <v>84.03603194620464</v>
+      </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
@@ -10797,15 +10985,33 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="14" t="n"/>
-      <c r="J8" s="14" t="n"/>
+      <c r="B8" s="14" t="n">
+        <v>0.8544</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0.8159</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0.6851</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>0.7302</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0.4795</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>0.6661</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>10.47040152304533</v>
+      </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -10838,15 +11044,33 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
-      <c r="J9" s="14" t="n"/>
+      <c r="B9" s="14" t="n">
+        <v>0.8587</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>0.7653</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0.7017</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0.7778</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>0.5239</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0.6836</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>9.209013861652336</v>
+      </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -11080,9 +11304,15 @@
       <c r="L14" s="15" t="n">
         <v>80.404</v>
       </c>
-      <c r="M14" s="8" t="n"/>
-      <c r="N14" s="8" t="n"/>
-      <c r="O14" s="8" t="n"/>
+      <c r="M14" s="15" t="n">
+        <v>60.52</v>
+      </c>
+      <c r="N14" s="15" t="n">
+        <v>76.20438550953283</v>
+      </c>
+      <c r="O14" s="15" t="n">
+        <v>75.33209637738319</v>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
@@ -11140,37 +11370,47 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.8425</v>
       </c>
       <c r="C16" s="14" t="n">
-        <v>0.8339</v>
+        <v>0.8375</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>0.6375</v>
+        <v>0.6344</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>0.6701</v>
+        <v>0.6796</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0.5939</v>
+        <v>0.5783</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>0.3686</v>
+        <v>0.3626</v>
       </c>
       <c r="H16" s="14" t="n">
-        <v>0.364</v>
+        <v>0.362</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>0.6166</v>
+        <v>0.6138</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>12.17765478688282</v>
-      </c>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="8" t="n"/>
-      <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n"/>
-      <c r="O16" s="8" t="n"/>
+        <v>11.90872614135452</v>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="L16" s="15" t="n">
+        <v>76.60600000000001</v>
+      </c>
+      <c r="M16" s="15" t="n">
+        <v>51.64</v>
+      </c>
+      <c r="N16" s="15" t="n">
+        <v>70.57294975750568</v>
+      </c>
+      <c r="O16" s="15" t="n">
+        <v>69.07973743937642</v>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -11178,20 +11418,48 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-      <c r="H17" s="14" t="n"/>
-      <c r="I17" s="14" t="n"/>
-      <c r="J17" s="14" t="n"/>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="8" t="n"/>
-      <c r="M17" s="8" t="n"/>
-      <c r="N17" s="8" t="n"/>
-      <c r="O17" s="8" t="n"/>
+      <c r="B17" s="14" t="n">
+        <v>0.8547</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>0.8339</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>0.6754</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>0.6756</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>0.6263</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>10.8883927478228</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>76.392</v>
+      </c>
+      <c r="M17" s="15" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="N17" s="15" t="n">
+        <v>74.94787703326428</v>
+      </c>
+      <c r="O17" s="15" t="n">
+        <v>69.58496925831606</v>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -11515,15 +11783,33 @@
           <t>2:4</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="14" t="n"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="14" t="n"/>
-      <c r="H24" s="14" t="n"/>
-      <c r="I24" s="14" t="n"/>
-      <c r="J24" s="14" t="n"/>
+      <c r="B24" s="14" t="n">
+        <v>0.8324</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>0.6237</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>0.6717</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>0.7214</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0.4582</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>0.6293</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>12.72611875397599</v>
+      </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -11556,15 +11842,33 @@
           <t>4:8</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="14" t="n"/>
-      <c r="E25" s="14" t="n"/>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="14" t="n"/>
-      <c r="H25" s="14" t="n"/>
-      <c r="I25" s="14" t="n"/>
-      <c r="J25" s="14" t="n"/>
+      <c r="B25" s="14" t="n">
+        <v>0.8416</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>0.6659</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>0.6922</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.7698</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0.5017</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>0.6556</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>11.53566840666572</v>
+      </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -11645,11 +11949,21 @@
       <c r="J27" s="14" t="n">
         <v>7.855145447281187</v>
       </c>
-      <c r="K27" s="7" t="n"/>
-      <c r="L27" s="7" t="n"/>
-      <c r="M27" s="7" t="n"/>
-      <c r="N27" s="7" t="n"/>
-      <c r="O27" s="7" t="n"/>
+      <c r="K27" s="14" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="L27" s="14" t="n">
+        <v>82.968</v>
+      </c>
+      <c r="M27" s="14" t="n">
+        <v>83.36</v>
+      </c>
+      <c r="N27" s="14" t="n">
+        <v>83.11612778481857</v>
+      </c>
+      <c r="O27" s="14" t="n">
+        <v>84.03603194620464</v>
+      </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
@@ -13181,11 +13495,21 @@
       <c r="J21" s="14" t="n">
         <v>7.855145447281187</v>
       </c>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="n"/>
-      <c r="O21" s="7" t="n"/>
+      <c r="K21" s="14" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>82.968</v>
+      </c>
+      <c r="M21" s="14" t="n">
+        <v>83.36</v>
+      </c>
+      <c r="N21" s="14" t="n">
+        <v>83.11612778481857</v>
+      </c>
+      <c r="O21" s="14" t="n">
+        <v>84.03603194620464</v>
+      </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
@@ -13193,22 +13517,48 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n"/>
-      <c r="C22" s="14" t="n"/>
-      <c r="D22" s="14" t="n"/>
-      <c r="E22" s="14" t="n"/>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="14" t="n"/>
-      <c r="H22" s="14" t="n"/>
-      <c r="I22" s="14" t="n"/>
+      <c r="B22" s="14" t="n">
+        <v>0.7813</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>0.8159</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>0.6253</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>0.6882</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>0.6987</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>0.4625</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>0.6363</v>
+      </c>
       <c r="J22" s="14" t="n">
         <v>9.555099798748797</v>
       </c>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="7" t="n"/>
-      <c r="N22" s="7" t="n"/>
-      <c r="O22" s="7" t="n"/>
+      <c r="K22" s="14" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>72.49399999999999</v>
+      </c>
+      <c r="M22" s="14" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="N22" s="14" t="n">
+        <v>68.76203701117156</v>
+      </c>
+      <c r="O22" s="14" t="n">
+        <v>64.07900925279289</v>
+      </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
@@ -13216,20 +13566,42 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="B23" s="14" t="n"/>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="14" t="n"/>
-      <c r="E23" s="14" t="n"/>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="14" t="n"/>
-      <c r="H23" s="14" t="n"/>
-      <c r="I23" s="14" t="n"/>
+      <c r="B23" s="14" t="n">
+        <v>0.4208</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>0.5306999999999999</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>0.5312</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>0.4004</v>
+      </c>
       <c r="J23" s="14" t="n">
         <v>27.57493867845532</v>
       </c>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
+      <c r="K23" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="N23" s="7" t="n"/>
       <c r="O23" s="7" t="n"/>
     </row>
@@ -13239,20 +13611,42 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="14" t="n"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="14" t="n"/>
-      <c r="H24" s="14" t="n"/>
-      <c r="I24" s="14" t="n"/>
+      <c r="B24" s="14" t="n">
+        <v>0.4147</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>0.5018</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>0.5051</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>0.3596</v>
+      </c>
       <c r="J24" s="14" t="n">
         <v>127.0739268153725</v>
       </c>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="7" t="n"/>
+      <c r="K24" s="14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="N24" s="7" t="n"/>
       <c r="O24" s="7" t="n"/>
     </row>
@@ -13262,20 +13656,42 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="14" t="n"/>
-      <c r="E25" s="14" t="n"/>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="14" t="n"/>
-      <c r="H25" s="14" t="n"/>
-      <c r="I25" s="14" t="n"/>
+      <c r="B25" s="14" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>0.5067</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0.2526</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>0.3525</v>
+      </c>
       <c r="J25" s="14" t="n">
         <v>1341.186220868133</v>
       </c>
-      <c r="K25" s="7" t="n"/>
-      <c r="L25" s="7" t="n"/>
-      <c r="M25" s="7" t="n"/>
+      <c r="K25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M25" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="N25" s="7" t="n"/>
       <c r="O25" s="7" t="n"/>
     </row>
@@ -16271,11 +16687,21 @@
       <c r="J21" s="14" t="n">
         <v>7.855145447281187</v>
       </c>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="n"/>
-      <c r="O21" s="7" t="n"/>
+      <c r="K21" s="14" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>82.968</v>
+      </c>
+      <c r="M21" s="14" t="n">
+        <v>83.36</v>
+      </c>
+      <c r="N21" s="14" t="n">
+        <v>83.11612778481857</v>
+      </c>
+      <c r="O21" s="14" t="n">
+        <v>84.03603194620464</v>
+      </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
@@ -16310,11 +16736,21 @@
       <c r="J22" s="14" t="n">
         <v>11.54656722841926</v>
       </c>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="7" t="n"/>
-      <c r="N22" s="7" t="n"/>
-      <c r="O22" s="7" t="n"/>
+      <c r="K22" s="14" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>62.956</v>
+      </c>
+      <c r="M22" s="14" t="n">
+        <v>48.64</v>
+      </c>
+      <c r="N22" s="14" t="n">
+        <v>52.20862859347312</v>
+      </c>
+      <c r="O22" s="14" t="n">
+        <v>57.87615714836828</v>
+      </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
@@ -16349,9 +16785,15 @@
       <c r="J23" s="14" t="n">
         <v>43.99941870370173</v>
       </c>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
+      <c r="K23" s="14" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="N23" s="7" t="n"/>
       <c r="O23" s="7" t="n"/>
     </row>
@@ -16388,9 +16830,15 @@
       <c r="J24" s="14" t="n">
         <v>200.3270629362775</v>
       </c>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="7" t="n"/>
+      <c r="K24" s="14" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="N24" s="7" t="n"/>
       <c r="O24" s="7" t="n"/>
     </row>
@@ -16427,8 +16875,12 @@
       <c r="J25" s="14" t="n">
         <v>1832.389631095462</v>
       </c>
-      <c r="K25" s="7" t="n"/>
-      <c r="L25" s="7" t="n"/>
+      <c r="K25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>0.005999999999999999</v>
+      </c>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n"/>
       <c r="O25" s="7" t="n"/>
@@ -19425,11 +19877,21 @@
       <c r="J21" s="14" t="n">
         <v>7.855145447281187</v>
       </c>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="n"/>
-      <c r="O21" s="7" t="n"/>
+      <c r="K21" s="14" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>82.968</v>
+      </c>
+      <c r="M21" s="14" t="n">
+        <v>83.36</v>
+      </c>
+      <c r="N21" s="14" t="n">
+        <v>83.11612778481857</v>
+      </c>
+      <c r="O21" s="14" t="n">
+        <v>84.03603194620464</v>
+      </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
@@ -19464,11 +19926,21 @@
       <c r="J22" s="14" t="n">
         <v>11.80012242122977</v>
       </c>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="7" t="n"/>
-      <c r="N22" s="7" t="n"/>
-      <c r="O22" s="7" t="n"/>
+      <c r="K22" s="14" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>75.908</v>
+      </c>
+      <c r="M22" s="14" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="N22" s="14" t="n">
+        <v>64.31969449485361</v>
+      </c>
+      <c r="O22" s="14" t="n">
+        <v>69.6219236237134</v>
+      </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
@@ -19503,7 +19975,9 @@
       <c r="J23" s="14" t="n">
         <v>92.03002914120208</v>
       </c>
-      <c r="K23" s="7" t="n"/>
+      <c r="K23" s="14" t="n">
+        <v>12</v>
+      </c>
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n"/>
@@ -22579,11 +23053,21 @@
       <c r="J21" s="14" t="n">
         <v>7.855145447281187</v>
       </c>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="n"/>
-      <c r="O21" s="7" t="n"/>
+      <c r="K21" s="14" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>82.968</v>
+      </c>
+      <c r="M21" s="14" t="n">
+        <v>83.36</v>
+      </c>
+      <c r="N21" s="14" t="n">
+        <v>83.11612778481857</v>
+      </c>
+      <c r="O21" s="14" t="n">
+        <v>84.03603194620464</v>
+      </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
